--- a/data/samples/HR_Current.xlsx
+++ b/data/samples/HR_Current.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C97BA13D-241E-4692-998C-1939EA67AFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{276C00FB-54C1-44EA-9C14-1FF62F03E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{B35A5613-5B32-42A3-89F3-C94ABABE9032}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="262">
   <si>
     <t>Employee Code</t>
   </si>
@@ -487,6 +487,339 @@
   </si>
   <si>
     <t>عبد العزيز حجيج رضيمان المرواني</t>
+  </si>
+  <si>
+    <t>MD Sahidul Islam</t>
+  </si>
+  <si>
+    <t>مد سيدول اسلام</t>
+  </si>
+  <si>
+    <t>الإشراف الداخلي - فندق ميسان روتانا المسك</t>
+  </si>
+  <si>
+    <t>Houseman</t>
+  </si>
+  <si>
+    <t>المدينة - الحربي</t>
+  </si>
+  <si>
+    <t>Samim Hossain</t>
+  </si>
+  <si>
+    <t>شميم اوسين</t>
+  </si>
+  <si>
+    <t>Md Hamidul Islam</t>
+  </si>
+  <si>
+    <t>مد حميد ال اسلام</t>
+  </si>
+  <si>
+    <t>Md Belal Hossen</t>
+  </si>
+  <si>
+    <t>مد حسين بلال</t>
+  </si>
+  <si>
+    <t>Md Sujib Mia</t>
+  </si>
+  <si>
+    <t>مد سوجيب مياه</t>
+  </si>
+  <si>
+    <t>الإشراف الداخلي - فندق ميسان التقوى</t>
+  </si>
+  <si>
+    <t>Morshed Alam</t>
+  </si>
+  <si>
+    <t>مرشد علام</t>
+  </si>
+  <si>
+    <t>SOHAG MIA</t>
+  </si>
+  <si>
+    <t>شوهاك مد عزيز الحكيم ميا</t>
+  </si>
+  <si>
+    <t>Anowar Hossain</t>
+  </si>
+  <si>
+    <t>انور اوسين</t>
+  </si>
+  <si>
+    <t>Md Rubel Miah</t>
+  </si>
+  <si>
+    <t>مد روبيل مياه</t>
+  </si>
+  <si>
+    <t>حاملي الحقائب - ميسان رحاب المسك</t>
+  </si>
+  <si>
+    <t>حامل حقائب</t>
+  </si>
+  <si>
+    <t>Zakir Hossain</t>
+  </si>
+  <si>
+    <t>زاكير اوسين</t>
+  </si>
+  <si>
+    <t>Md Sahajahan</t>
+  </si>
+  <si>
+    <t>مد شاه جهان</t>
+  </si>
+  <si>
+    <t>Md Jamil Hossen</t>
+  </si>
+  <si>
+    <t>مد جميل حسين</t>
+  </si>
+  <si>
+    <t>Sohel Sayedol Hoque</t>
+  </si>
+  <si>
+    <t>سهيل سعيد هوكي هوكي</t>
+  </si>
+  <si>
+    <t>Muhammad Meer Hossion</t>
+  </si>
+  <si>
+    <t>محمد مير حوسيون</t>
+  </si>
+  <si>
+    <t>Foaiz Ullah</t>
+  </si>
+  <si>
+    <t>فيض الله</t>
+  </si>
+  <si>
+    <t>Md Roman Miah</t>
+  </si>
+  <si>
+    <t>مد رومان مياه</t>
+  </si>
+  <si>
+    <t>Md Rahad</t>
+  </si>
+  <si>
+    <t>مد راهاد راهاد مد</t>
+  </si>
+  <si>
+    <t>MD Shahidul Islam</t>
+  </si>
+  <si>
+    <t>مد شهيد الاسلام</t>
+  </si>
+  <si>
+    <t>المدينة - موارد</t>
+  </si>
+  <si>
+    <t>Estiek Hossain</t>
+  </si>
+  <si>
+    <t>اشتياق حسين</t>
+  </si>
+  <si>
+    <t>MD Somon Miah</t>
+  </si>
+  <si>
+    <t>مد شمون مياه</t>
+  </si>
+  <si>
+    <t>المدينة - جبل احد</t>
+  </si>
+  <si>
+    <t>Mohammed Yeasin Arafat</t>
+  </si>
+  <si>
+    <t>محمد ياسين عرفات</t>
+  </si>
+  <si>
+    <t>Naim Howlader</t>
+  </si>
+  <si>
+    <t>نعيم حولادر</t>
+  </si>
+  <si>
+    <t>Md Alamin Mia</t>
+  </si>
+  <si>
+    <t>محمد لامين ميا</t>
+  </si>
+  <si>
+    <t>MD Mizanur Rahman</t>
+  </si>
+  <si>
+    <t>مد ميزان نور رحمن</t>
+  </si>
+  <si>
+    <t>Rakib Hossain</t>
+  </si>
+  <si>
+    <t>رقيب حسين</t>
+  </si>
+  <si>
+    <t>MD Faruq</t>
+  </si>
+  <si>
+    <t>مد قاروق</t>
+  </si>
+  <si>
+    <t>Ahmadulla Mamun</t>
+  </si>
+  <si>
+    <t>أحمد الله مامون</t>
+  </si>
+  <si>
+    <t>Mohammad Jihad Hossain</t>
+  </si>
+  <si>
+    <t>محمد جهاد حسين</t>
+  </si>
+  <si>
+    <t>Alamin Abo Taher</t>
+  </si>
+  <si>
+    <t>الامين ابو الطاهر</t>
+  </si>
+  <si>
+    <t>MD Nobibur Rahman</t>
+  </si>
+  <si>
+    <t>مد نوبيب ال رحمن</t>
+  </si>
+  <si>
+    <t>MD Joynal Mia</t>
+  </si>
+  <si>
+    <t>مد جونيال ميا</t>
+  </si>
+  <si>
+    <t>MD Ahnaf</t>
+  </si>
+  <si>
+    <t>مد احناف</t>
+  </si>
+  <si>
+    <t>حاملي الحقائب - فندق ميسان روتانا المسك</t>
+  </si>
+  <si>
+    <t>المدينة - ارض النظافة</t>
+  </si>
+  <si>
+    <t>Shahriar Nawas</t>
+  </si>
+  <si>
+    <t>شهريار نواز</t>
+  </si>
+  <si>
+    <t>Sarif Hannan</t>
+  </si>
+  <si>
+    <t>شريف حنان</t>
+  </si>
+  <si>
+    <t>Junaed Md Jamir Ali</t>
+  </si>
+  <si>
+    <t>جوند محمد جامير علي علي</t>
+  </si>
+  <si>
+    <t>Md Shakhawat Hossain</t>
+  </si>
+  <si>
+    <t>مد شخوات اوسين</t>
+  </si>
+  <si>
+    <t>Md Al Amin</t>
+  </si>
+  <si>
+    <t>مد ال أمين</t>
+  </si>
+  <si>
+    <t>Md Shakil Rana</t>
+  </si>
+  <si>
+    <t>مد شكيل رنا</t>
+  </si>
+  <si>
+    <t>Alif Hasan Rabby</t>
+  </si>
+  <si>
+    <t>اليف حسان ربي</t>
+  </si>
+  <si>
+    <t>Md Uzzal Mia</t>
+  </si>
+  <si>
+    <t>مد اوزال ميا</t>
+  </si>
+  <si>
+    <t>Mohammad Abu Tahar</t>
+  </si>
+  <si>
+    <t>محمد ابو طاهر ابو طاهر طاهر</t>
+  </si>
+  <si>
+    <t>Md Jishan</t>
+  </si>
+  <si>
+    <t>مد جيشان</t>
+  </si>
+  <si>
+    <t>Faysal Pathan</t>
+  </si>
+  <si>
+    <t>فيصل باثين كاشم باتهان</t>
+  </si>
+  <si>
+    <t>Mohammad Monir</t>
+  </si>
+  <si>
+    <t>محمد منير</t>
+  </si>
+  <si>
+    <t>MOHAMMAD HUMAYUN</t>
+  </si>
+  <si>
+    <t>محمد هومايون منصور علي</t>
+  </si>
+  <si>
+    <t>Asst. Catering Manager</t>
+  </si>
+  <si>
+    <t>MD Shakayet Turaz</t>
+  </si>
+  <si>
+    <t>مد شاكيت توراز</t>
+  </si>
+  <si>
+    <t>Saif Al Mohamed Islam Islam</t>
+  </si>
+  <si>
+    <t>سيف ال محمد اسلام اسلام</t>
+  </si>
+  <si>
+    <t>AHAMMAD ALI MAFIJ UDDIN</t>
+  </si>
+  <si>
+    <t>احمد علي مفيض دين</t>
+  </si>
+  <si>
+    <t>SAFIULLAH ABDUL KADIR</t>
+  </si>
+  <si>
+    <t>صفي الله عبد ال قادر</t>
+  </si>
+  <si>
+    <t>Sakawat Hossen</t>
+  </si>
+  <si>
+    <t>سخاوات اوسين</t>
   </si>
 </sst>
 </file>
@@ -840,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883B3F3C-5A92-453D-9638-D2640977E06C}">
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -3262,6 +3595,2704 @@
         <v>25</v>
       </c>
     </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>2651</v>
+      </c>
+      <c r="C48" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" t="s">
+        <v>154</v>
+      </c>
+      <c r="I48">
+        <v>2800</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" t="s">
+        <v>40</v>
+      </c>
+      <c r="N48" s="1">
+        <v>46244</v>
+      </c>
+      <c r="P48" s="1">
+        <v>46243</v>
+      </c>
+      <c r="R48" s="1">
+        <v>46006</v>
+      </c>
+      <c r="T48" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>6126</v>
+      </c>
+      <c r="C49" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" t="s">
+        <v>38</v>
+      </c>
+      <c r="H49" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49">
+        <v>2800</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" t="s">
+        <v>40</v>
+      </c>
+      <c r="N49" s="1">
+        <v>45645</v>
+      </c>
+      <c r="O49" s="1">
+        <v>46009</v>
+      </c>
+      <c r="P49" s="1">
+        <v>45734</v>
+      </c>
+      <c r="R49" s="1">
+        <v>45673</v>
+      </c>
+      <c r="T49" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>6127</v>
+      </c>
+      <c r="C50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>37</v>
+      </c>
+      <c r="G50" t="s">
+        <v>38</v>
+      </c>
+      <c r="H50" t="s">
+        <v>154</v>
+      </c>
+      <c r="I50">
+        <v>2800</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" t="s">
+        <v>40</v>
+      </c>
+      <c r="N50" s="1">
+        <v>45645</v>
+      </c>
+      <c r="O50" s="1">
+        <v>46009</v>
+      </c>
+      <c r="P50" s="1">
+        <v>45734</v>
+      </c>
+      <c r="R50" s="1">
+        <v>45006</v>
+      </c>
+      <c r="T50" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>6129</v>
+      </c>
+      <c r="C51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51">
+        <v>6</v>
+      </c>
+      <c r="F51" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" t="s">
+        <v>38</v>
+      </c>
+      <c r="H51" t="s">
+        <v>154</v>
+      </c>
+      <c r="I51">
+        <v>2800</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" t="s">
+        <v>40</v>
+      </c>
+      <c r="N51" s="1">
+        <v>45901</v>
+      </c>
+      <c r="O51" s="1">
+        <v>46265</v>
+      </c>
+      <c r="P51" s="1">
+        <v>45990</v>
+      </c>
+      <c r="R51" s="1">
+        <v>46250</v>
+      </c>
+      <c r="T51" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>6145</v>
+      </c>
+      <c r="C52" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" t="s">
+        <v>163</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" t="s">
+        <v>164</v>
+      </c>
+      <c r="H52" t="s">
+        <v>154</v>
+      </c>
+      <c r="I52">
+        <v>2800</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" t="s">
+        <v>40</v>
+      </c>
+      <c r="N52" s="1">
+        <v>45901</v>
+      </c>
+      <c r="O52" s="1">
+        <v>46265</v>
+      </c>
+      <c r="P52" s="1">
+        <v>45990</v>
+      </c>
+      <c r="R52" s="1">
+        <v>45661</v>
+      </c>
+      <c r="S52" s="1">
+        <v>48992</v>
+      </c>
+      <c r="T52" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>6122</v>
+      </c>
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+      <c r="F53" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H53" t="s">
+        <v>154</v>
+      </c>
+      <c r="I53">
+        <v>2800</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" t="s">
+        <v>40</v>
+      </c>
+      <c r="N53" s="1">
+        <v>45645</v>
+      </c>
+      <c r="O53" s="1">
+        <v>46009</v>
+      </c>
+      <c r="P53" s="1">
+        <v>45734</v>
+      </c>
+      <c r="R53" s="1">
+        <v>46361</v>
+      </c>
+      <c r="T53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>6120</v>
+      </c>
+      <c r="C54" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+      <c r="F54" t="s">
+        <v>37</v>
+      </c>
+      <c r="G54" t="s">
+        <v>38</v>
+      </c>
+      <c r="H54" t="s">
+        <v>154</v>
+      </c>
+      <c r="I54">
+        <v>2800</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="1">
+        <v>45645</v>
+      </c>
+      <c r="O54" s="1">
+        <v>46009</v>
+      </c>
+      <c r="P54" s="1">
+        <v>45734</v>
+      </c>
+      <c r="R54" s="1">
+        <v>45698</v>
+      </c>
+      <c r="T54" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>6092</v>
+      </c>
+      <c r="C55" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" t="s">
+        <v>66</v>
+      </c>
+      <c r="G55" t="s">
+        <v>164</v>
+      </c>
+      <c r="H55" t="s">
+        <v>154</v>
+      </c>
+      <c r="I55">
+        <v>2800</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>23</v>
+      </c>
+      <c r="M55" t="s">
+        <v>40</v>
+      </c>
+      <c r="N55" s="1">
+        <v>45637</v>
+      </c>
+      <c r="O55" s="1">
+        <v>46001</v>
+      </c>
+      <c r="P55" s="1">
+        <v>45726</v>
+      </c>
+      <c r="R55" s="1">
+        <v>44933</v>
+      </c>
+      <c r="T55" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>6086</v>
+      </c>
+      <c r="C56" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56" t="s">
+        <v>172</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+      <c r="F56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" t="s">
+        <v>174</v>
+      </c>
+      <c r="I56">
+        <v>2800</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56" t="s">
+        <v>23</v>
+      </c>
+      <c r="M56" t="s">
+        <v>40</v>
+      </c>
+      <c r="N56" s="1">
+        <v>45641</v>
+      </c>
+      <c r="O56" s="1">
+        <v>46005</v>
+      </c>
+      <c r="P56" s="1">
+        <v>45730</v>
+      </c>
+      <c r="R56" s="1">
+        <v>46794</v>
+      </c>
+      <c r="S56" s="1">
+        <v>49191</v>
+      </c>
+      <c r="T56" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>6085</v>
+      </c>
+      <c r="C57" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57" t="s">
+        <v>176</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+      <c r="F57" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" t="s">
+        <v>173</v>
+      </c>
+      <c r="H57" t="s">
+        <v>174</v>
+      </c>
+      <c r="I57">
+        <v>2800</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" t="s">
+        <v>40</v>
+      </c>
+      <c r="N57" s="1">
+        <v>45641</v>
+      </c>
+      <c r="O57" s="1">
+        <v>46005</v>
+      </c>
+      <c r="P57" s="1">
+        <v>45730</v>
+      </c>
+      <c r="R57" s="1">
+        <v>46008</v>
+      </c>
+      <c r="S57" s="1">
+        <v>48099</v>
+      </c>
+      <c r="T57" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>5995</v>
+      </c>
+      <c r="C58" t="s">
+        <v>177</v>
+      </c>
+      <c r="D58" t="s">
+        <v>178</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+      <c r="F58" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" t="s">
+        <v>154</v>
+      </c>
+      <c r="I58">
+        <v>2800</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" t="s">
+        <v>40</v>
+      </c>
+      <c r="N58" s="1">
+        <v>45583</v>
+      </c>
+      <c r="O58" s="1">
+        <v>45947</v>
+      </c>
+      <c r="P58" s="1">
+        <v>45672</v>
+      </c>
+      <c r="R58" s="1">
+        <v>45652</v>
+      </c>
+      <c r="T58" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>5993</v>
+      </c>
+      <c r="C59" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59" t="s">
+        <v>32</v>
+      </c>
+      <c r="G59" t="s">
+        <v>43</v>
+      </c>
+      <c r="H59" t="s">
+        <v>154</v>
+      </c>
+      <c r="I59">
+        <v>2800</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" t="s">
+        <v>40</v>
+      </c>
+      <c r="N59" s="1">
+        <v>45569</v>
+      </c>
+      <c r="O59" s="1">
+        <v>45933</v>
+      </c>
+      <c r="P59" s="1">
+        <v>45658</v>
+      </c>
+      <c r="R59" s="1">
+        <v>45652</v>
+      </c>
+      <c r="S59" s="1">
+        <v>48876</v>
+      </c>
+      <c r="T59" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>5961</v>
+      </c>
+      <c r="C60" t="s">
+        <v>181</v>
+      </c>
+      <c r="D60" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60">
+        <v>6</v>
+      </c>
+      <c r="F60" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" t="s">
+        <v>38</v>
+      </c>
+      <c r="H60" t="s">
+        <v>154</v>
+      </c>
+      <c r="I60">
+        <v>2800</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" t="s">
+        <v>40</v>
+      </c>
+      <c r="N60" s="1">
+        <v>45536</v>
+      </c>
+      <c r="O60" s="1">
+        <v>45900</v>
+      </c>
+      <c r="P60" s="1">
+        <v>45625</v>
+      </c>
+      <c r="R60" s="1">
+        <v>45783</v>
+      </c>
+      <c r="T60" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>5830</v>
+      </c>
+      <c r="C61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61">
+        <v>6</v>
+      </c>
+      <c r="F61" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" t="s">
+        <v>173</v>
+      </c>
+      <c r="H61" t="s">
+        <v>174</v>
+      </c>
+      <c r="I61">
+        <v>2800</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>23</v>
+      </c>
+      <c r="M61" t="s">
+        <v>40</v>
+      </c>
+      <c r="N61" s="1">
+        <v>45515</v>
+      </c>
+      <c r="O61" s="1">
+        <v>45879</v>
+      </c>
+      <c r="P61" s="1">
+        <v>45604</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>46323</v>
+      </c>
+      <c r="R61" s="1">
+        <v>45979</v>
+      </c>
+      <c r="T61" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>5773</v>
+      </c>
+      <c r="C62" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
+        <v>186</v>
+      </c>
+      <c r="E62">
+        <v>6</v>
+      </c>
+      <c r="F62" t="s">
+        <v>37</v>
+      </c>
+      <c r="G62" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" t="s">
+        <v>154</v>
+      </c>
+      <c r="I62">
+        <v>2800</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>23</v>
+      </c>
+      <c r="M62" t="s">
+        <v>40</v>
+      </c>
+      <c r="N62" s="1">
+        <v>45485</v>
+      </c>
+      <c r="O62" s="1">
+        <v>45849</v>
+      </c>
+      <c r="P62" s="1">
+        <v>45574</v>
+      </c>
+      <c r="R62" s="1">
+        <v>45661</v>
+      </c>
+      <c r="T62" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>6461</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+      <c r="E63">
+        <v>6</v>
+      </c>
+      <c r="F63" t="s">
+        <v>32</v>
+      </c>
+      <c r="G63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" t="s">
+        <v>154</v>
+      </c>
+      <c r="I63">
+        <v>2800</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>23</v>
+      </c>
+      <c r="M63" t="s">
+        <v>40</v>
+      </c>
+      <c r="N63" s="1">
+        <v>45854</v>
+      </c>
+      <c r="O63" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P63" s="1">
+        <v>45943</v>
+      </c>
+      <c r="R63" s="1">
+        <v>45858</v>
+      </c>
+      <c r="T63" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>5484</v>
+      </c>
+      <c r="C64" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" t="s">
+        <v>190</v>
+      </c>
+      <c r="E64">
+        <v>6</v>
+      </c>
+      <c r="F64" t="s">
+        <v>37</v>
+      </c>
+      <c r="G64" t="s">
+        <v>173</v>
+      </c>
+      <c r="H64" t="s">
+        <v>174</v>
+      </c>
+      <c r="I64">
+        <v>2800</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
+        <v>23</v>
+      </c>
+      <c r="M64" t="s">
+        <v>40</v>
+      </c>
+      <c r="N64" s="1">
+        <v>45216</v>
+      </c>
+      <c r="O64" s="1">
+        <v>45581</v>
+      </c>
+      <c r="P64" s="1">
+        <v>45305</v>
+      </c>
+      <c r="R64" s="1">
+        <v>45117</v>
+      </c>
+      <c r="T64" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>6589</v>
+      </c>
+      <c r="C65" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" t="s">
+        <v>192</v>
+      </c>
+      <c r="E65">
+        <v>6</v>
+      </c>
+      <c r="F65" t="s">
+        <v>37</v>
+      </c>
+      <c r="G65" t="s">
+        <v>38</v>
+      </c>
+      <c r="H65" t="s">
+        <v>154</v>
+      </c>
+      <c r="I65">
+        <v>2800</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>23</v>
+      </c>
+      <c r="M65" t="s">
+        <v>40</v>
+      </c>
+      <c r="N65" s="1">
+        <v>45874</v>
+      </c>
+      <c r="O65" s="1">
+        <v>46238</v>
+      </c>
+      <c r="P65" s="1">
+        <v>45963</v>
+      </c>
+      <c r="S65" s="1">
+        <v>48500</v>
+      </c>
+      <c r="T65" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>5128</v>
+      </c>
+      <c r="C66" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66">
+        <v>6</v>
+      </c>
+      <c r="F66" t="s">
+        <v>66</v>
+      </c>
+      <c r="G66" t="s">
+        <v>164</v>
+      </c>
+      <c r="H66" t="s">
+        <v>154</v>
+      </c>
+      <c r="I66">
+        <v>2800</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
+        <v>23</v>
+      </c>
+      <c r="M66" t="s">
+        <v>40</v>
+      </c>
+      <c r="N66" s="1">
+        <v>44808</v>
+      </c>
+      <c r="O66" s="1">
+        <v>45172</v>
+      </c>
+      <c r="P66" s="1">
+        <v>44898</v>
+      </c>
+      <c r="R66" s="1">
+        <v>46319</v>
+      </c>
+      <c r="T66" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>6675</v>
+      </c>
+      <c r="C67" t="s">
+        <v>196</v>
+      </c>
+      <c r="D67" t="s">
+        <v>197</v>
+      </c>
+      <c r="E67">
+        <v>6</v>
+      </c>
+      <c r="F67" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" t="s">
+        <v>43</v>
+      </c>
+      <c r="H67" t="s">
+        <v>154</v>
+      </c>
+      <c r="I67">
+        <v>2800</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" t="s">
+        <v>40</v>
+      </c>
+      <c r="N67" s="1">
+        <v>46204</v>
+      </c>
+      <c r="P67" s="1">
+        <v>46203</v>
+      </c>
+      <c r="T67" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>2650</v>
+      </c>
+      <c r="C68" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68" t="s">
+        <v>200</v>
+      </c>
+      <c r="E68">
+        <v>6</v>
+      </c>
+      <c r="F68" t="s">
+        <v>46</v>
+      </c>
+      <c r="G68" t="s">
+        <v>153</v>
+      </c>
+      <c r="H68" t="s">
+        <v>154</v>
+      </c>
+      <c r="I68">
+        <v>2800</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" t="s">
+        <v>40</v>
+      </c>
+      <c r="N68" s="1">
+        <v>46244</v>
+      </c>
+      <c r="P68" s="1">
+        <v>46243</v>
+      </c>
+      <c r="R68" s="1">
+        <v>46216</v>
+      </c>
+      <c r="T68" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>2649</v>
+      </c>
+      <c r="C69" t="s">
+        <v>201</v>
+      </c>
+      <c r="D69" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69">
+        <v>6</v>
+      </c>
+      <c r="F69" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" t="s">
+        <v>153</v>
+      </c>
+      <c r="H69" t="s">
+        <v>154</v>
+      </c>
+      <c r="I69">
+        <v>2800</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>23</v>
+      </c>
+      <c r="M69" t="s">
+        <v>40</v>
+      </c>
+      <c r="N69" s="1">
+        <v>46244</v>
+      </c>
+      <c r="P69" s="1">
+        <v>46243</v>
+      </c>
+      <c r="R69" s="1">
+        <v>45729</v>
+      </c>
+      <c r="T69" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>6166</v>
+      </c>
+      <c r="C70" t="s">
+        <v>203</v>
+      </c>
+      <c r="D70" t="s">
+        <v>204</v>
+      </c>
+      <c r="E70">
+        <v>6</v>
+      </c>
+      <c r="F70" t="s">
+        <v>32</v>
+      </c>
+      <c r="G70" t="s">
+        <v>43</v>
+      </c>
+      <c r="H70" t="s">
+        <v>154</v>
+      </c>
+      <c r="I70">
+        <v>2800</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>23</v>
+      </c>
+      <c r="M70" t="s">
+        <v>40</v>
+      </c>
+      <c r="N70" s="1">
+        <v>45658</v>
+      </c>
+      <c r="O70" s="1">
+        <v>46022</v>
+      </c>
+      <c r="P70" s="1">
+        <v>45747</v>
+      </c>
+      <c r="R70" s="1">
+        <v>45661</v>
+      </c>
+      <c r="T70" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7287</v>
+      </c>
+      <c r="C71" t="s">
+        <v>205</v>
+      </c>
+      <c r="D71" t="s">
+        <v>206</v>
+      </c>
+      <c r="E71">
+        <v>6</v>
+      </c>
+      <c r="F71" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" t="s">
+        <v>153</v>
+      </c>
+      <c r="H71" t="s">
+        <v>154</v>
+      </c>
+      <c r="I71">
+        <v>2800</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>23</v>
+      </c>
+      <c r="M71" t="s">
+        <v>40</v>
+      </c>
+      <c r="N71" s="1">
+        <v>46223</v>
+      </c>
+      <c r="P71" s="1">
+        <v>46222</v>
+      </c>
+      <c r="T71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7288</v>
+      </c>
+      <c r="C72" t="s">
+        <v>207</v>
+      </c>
+      <c r="D72" t="s">
+        <v>208</v>
+      </c>
+      <c r="E72">
+        <v>6</v>
+      </c>
+      <c r="F72" t="s">
+        <v>46</v>
+      </c>
+      <c r="G72" t="s">
+        <v>153</v>
+      </c>
+      <c r="H72" t="s">
+        <v>154</v>
+      </c>
+      <c r="I72">
+        <v>2800</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" t="s">
+        <v>40</v>
+      </c>
+      <c r="N72" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P72" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7289</v>
+      </c>
+      <c r="C73" t="s">
+        <v>209</v>
+      </c>
+      <c r="D73" t="s">
+        <v>210</v>
+      </c>
+      <c r="E73">
+        <v>6</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="s">
+        <v>153</v>
+      </c>
+      <c r="H73" t="s">
+        <v>154</v>
+      </c>
+      <c r="I73">
+        <v>2800</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>23</v>
+      </c>
+      <c r="M73" t="s">
+        <v>40</v>
+      </c>
+      <c r="N73" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P73" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T73" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7291</v>
+      </c>
+      <c r="C74" t="s">
+        <v>211</v>
+      </c>
+      <c r="D74" t="s">
+        <v>212</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74" t="s">
+        <v>46</v>
+      </c>
+      <c r="G74" t="s">
+        <v>153</v>
+      </c>
+      <c r="H74" t="s">
+        <v>154</v>
+      </c>
+      <c r="I74">
+        <v>2800</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>23</v>
+      </c>
+      <c r="M74" t="s">
+        <v>40</v>
+      </c>
+      <c r="N74" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P74" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7292</v>
+      </c>
+      <c r="C75" t="s">
+        <v>213</v>
+      </c>
+      <c r="D75" t="s">
+        <v>214</v>
+      </c>
+      <c r="E75">
+        <v>6</v>
+      </c>
+      <c r="F75" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" t="s">
+        <v>153</v>
+      </c>
+      <c r="H75" t="s">
+        <v>154</v>
+      </c>
+      <c r="I75">
+        <v>2800</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>23</v>
+      </c>
+      <c r="M75" t="s">
+        <v>40</v>
+      </c>
+      <c r="N75" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P75" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T75" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7293</v>
+      </c>
+      <c r="C76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" t="s">
+        <v>216</v>
+      </c>
+      <c r="E76">
+        <v>6</v>
+      </c>
+      <c r="F76" t="s">
+        <v>46</v>
+      </c>
+      <c r="G76" t="s">
+        <v>153</v>
+      </c>
+      <c r="H76" t="s">
+        <v>154</v>
+      </c>
+      <c r="I76">
+        <v>2800</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>23</v>
+      </c>
+      <c r="M76" t="s">
+        <v>40</v>
+      </c>
+      <c r="N76" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P76" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T76" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7294</v>
+      </c>
+      <c r="C77" t="s">
+        <v>217</v>
+      </c>
+      <c r="D77" t="s">
+        <v>218</v>
+      </c>
+      <c r="E77">
+        <v>6</v>
+      </c>
+      <c r="F77" t="s">
+        <v>37</v>
+      </c>
+      <c r="G77" t="s">
+        <v>38</v>
+      </c>
+      <c r="H77" t="s">
+        <v>154</v>
+      </c>
+      <c r="I77">
+        <v>2800</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>23</v>
+      </c>
+      <c r="M77" t="s">
+        <v>40</v>
+      </c>
+      <c r="N77" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P77" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T77" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7295</v>
+      </c>
+      <c r="C78" t="s">
+        <v>219</v>
+      </c>
+      <c r="D78" t="s">
+        <v>220</v>
+      </c>
+      <c r="E78">
+        <v>6</v>
+      </c>
+      <c r="F78" t="s">
+        <v>46</v>
+      </c>
+      <c r="G78" t="s">
+        <v>153</v>
+      </c>
+      <c r="H78" t="s">
+        <v>154</v>
+      </c>
+      <c r="I78">
+        <v>2800</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>23</v>
+      </c>
+      <c r="M78" t="s">
+        <v>40</v>
+      </c>
+      <c r="N78" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P78" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T78" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7300</v>
+      </c>
+      <c r="C79" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" t="s">
+        <v>222</v>
+      </c>
+      <c r="E79">
+        <v>6</v>
+      </c>
+      <c r="F79" t="s">
+        <v>46</v>
+      </c>
+      <c r="G79" t="s">
+        <v>223</v>
+      </c>
+      <c r="H79" t="s">
+        <v>174</v>
+      </c>
+      <c r="I79">
+        <v>2800</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" t="s">
+        <v>40</v>
+      </c>
+      <c r="N79" s="1">
+        <v>46218</v>
+      </c>
+      <c r="O79" s="1">
+        <v>46582</v>
+      </c>
+      <c r="P79" s="1">
+        <v>46307</v>
+      </c>
+      <c r="T79" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7301</v>
+      </c>
+      <c r="C80" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" t="s">
+        <v>226</v>
+      </c>
+      <c r="E80">
+        <v>6</v>
+      </c>
+      <c r="F80" t="s">
+        <v>46</v>
+      </c>
+      <c r="G80" t="s">
+        <v>223</v>
+      </c>
+      <c r="H80" t="s">
+        <v>174</v>
+      </c>
+      <c r="I80">
+        <v>2800</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>23</v>
+      </c>
+      <c r="M80" t="s">
+        <v>40</v>
+      </c>
+      <c r="N80" s="1">
+        <v>46218</v>
+      </c>
+      <c r="P80" s="1">
+        <v>46217</v>
+      </c>
+      <c r="T80" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7302</v>
+      </c>
+      <c r="C81" t="s">
+        <v>227</v>
+      </c>
+      <c r="D81" t="s">
+        <v>228</v>
+      </c>
+      <c r="E81">
+        <v>6</v>
+      </c>
+      <c r="F81" t="s">
+        <v>46</v>
+      </c>
+      <c r="G81" t="s">
+        <v>223</v>
+      </c>
+      <c r="H81" t="s">
+        <v>174</v>
+      </c>
+      <c r="I81">
+        <v>2800</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>23</v>
+      </c>
+      <c r="M81" t="s">
+        <v>40</v>
+      </c>
+      <c r="N81" s="1">
+        <v>46218</v>
+      </c>
+      <c r="P81" s="1">
+        <v>46217</v>
+      </c>
+      <c r="T81" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>6233</v>
+      </c>
+      <c r="C82" t="s">
+        <v>229</v>
+      </c>
+      <c r="D82" t="s">
+        <v>230</v>
+      </c>
+      <c r="E82">
+        <v>6</v>
+      </c>
+      <c r="F82" t="s">
+        <v>66</v>
+      </c>
+      <c r="G82" t="s">
+        <v>164</v>
+      </c>
+      <c r="H82" t="s">
+        <v>154</v>
+      </c>
+      <c r="I82">
+        <v>2800</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82" t="s">
+        <v>40</v>
+      </c>
+      <c r="N82" s="1">
+        <v>45717</v>
+      </c>
+      <c r="O82" s="1">
+        <v>46081</v>
+      </c>
+      <c r="P82" s="1">
+        <v>45806</v>
+      </c>
+      <c r="R82" s="1">
+        <v>45719</v>
+      </c>
+      <c r="T82" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>6234</v>
+      </c>
+      <c r="C83" t="s">
+        <v>231</v>
+      </c>
+      <c r="D83" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83">
+        <v>6</v>
+      </c>
+      <c r="F83" t="s">
+        <v>66</v>
+      </c>
+      <c r="G83" t="s">
+        <v>164</v>
+      </c>
+      <c r="H83" t="s">
+        <v>154</v>
+      </c>
+      <c r="I83">
+        <v>2800</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>23</v>
+      </c>
+      <c r="M83" t="s">
+        <v>40</v>
+      </c>
+      <c r="N83" s="1">
+        <v>45717</v>
+      </c>
+      <c r="O83" s="1">
+        <v>46081</v>
+      </c>
+      <c r="P83" s="1">
+        <v>45806</v>
+      </c>
+      <c r="R83" s="1">
+        <v>45746</v>
+      </c>
+      <c r="T83" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>6235</v>
+      </c>
+      <c r="C84" t="s">
+        <v>233</v>
+      </c>
+      <c r="D84" t="s">
+        <v>234</v>
+      </c>
+      <c r="E84">
+        <v>6</v>
+      </c>
+      <c r="F84" t="s">
+        <v>66</v>
+      </c>
+      <c r="G84" t="s">
+        <v>164</v>
+      </c>
+      <c r="H84" t="s">
+        <v>154</v>
+      </c>
+      <c r="I84">
+        <v>2800</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" t="s">
+        <v>40</v>
+      </c>
+      <c r="N84" s="1">
+        <v>45717</v>
+      </c>
+      <c r="O84" s="1">
+        <v>46081</v>
+      </c>
+      <c r="P84" s="1">
+        <v>45806</v>
+      </c>
+      <c r="R84" s="1">
+        <v>45718</v>
+      </c>
+      <c r="T84" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>6236</v>
+      </c>
+      <c r="C85" t="s">
+        <v>235</v>
+      </c>
+      <c r="D85" t="s">
+        <v>236</v>
+      </c>
+      <c r="E85">
+        <v>6</v>
+      </c>
+      <c r="F85" t="s">
+        <v>66</v>
+      </c>
+      <c r="G85" t="s">
+        <v>164</v>
+      </c>
+      <c r="H85" t="s">
+        <v>154</v>
+      </c>
+      <c r="I85">
+        <v>2800</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>23</v>
+      </c>
+      <c r="M85" t="s">
+        <v>40</v>
+      </c>
+      <c r="N85" s="1">
+        <v>45717</v>
+      </c>
+      <c r="O85" s="1">
+        <v>46081</v>
+      </c>
+      <c r="P85" s="1">
+        <v>45806</v>
+      </c>
+      <c r="R85" s="1">
+        <v>45440</v>
+      </c>
+      <c r="T85" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>6237</v>
+      </c>
+      <c r="C86" t="s">
+        <v>237</v>
+      </c>
+      <c r="D86" t="s">
+        <v>238</v>
+      </c>
+      <c r="E86">
+        <v>6</v>
+      </c>
+      <c r="F86" t="s">
+        <v>66</v>
+      </c>
+      <c r="G86" t="s">
+        <v>164</v>
+      </c>
+      <c r="H86" t="s">
+        <v>154</v>
+      </c>
+      <c r="I86">
+        <v>2800</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>23</v>
+      </c>
+      <c r="M86" t="s">
+        <v>40</v>
+      </c>
+      <c r="N86" s="1">
+        <v>45717</v>
+      </c>
+      <c r="O86" s="1">
+        <v>46081</v>
+      </c>
+      <c r="P86" s="1">
+        <v>45806</v>
+      </c>
+      <c r="R86" s="1">
+        <v>46089</v>
+      </c>
+      <c r="T86" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>6450</v>
+      </c>
+      <c r="C87" t="s">
+        <v>239</v>
+      </c>
+      <c r="D87" t="s">
+        <v>240</v>
+      </c>
+      <c r="E87">
+        <v>6</v>
+      </c>
+      <c r="F87" t="s">
+        <v>66</v>
+      </c>
+      <c r="G87" t="s">
+        <v>164</v>
+      </c>
+      <c r="H87" t="s">
+        <v>154</v>
+      </c>
+      <c r="I87">
+        <v>2800</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M87" t="s">
+        <v>40</v>
+      </c>
+      <c r="N87" s="1">
+        <v>45854</v>
+      </c>
+      <c r="O87" s="1">
+        <v>46218</v>
+      </c>
+      <c r="P87" s="1">
+        <v>45943</v>
+      </c>
+      <c r="T87" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>6455</v>
+      </c>
+      <c r="C88" t="s">
+        <v>241</v>
+      </c>
+      <c r="D88" t="s">
+        <v>242</v>
+      </c>
+      <c r="E88">
+        <v>6</v>
+      </c>
+      <c r="F88" t="s">
+        <v>66</v>
+      </c>
+      <c r="G88" t="s">
+        <v>164</v>
+      </c>
+      <c r="H88" t="s">
+        <v>154</v>
+      </c>
+      <c r="I88">
+        <v>2800</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88" t="s">
+        <v>40</v>
+      </c>
+      <c r="N88" s="1">
+        <v>45854</v>
+      </c>
+      <c r="O88" s="1">
+        <v>46218</v>
+      </c>
+      <c r="P88" s="1">
+        <v>45943</v>
+      </c>
+      <c r="T88" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>6459</v>
+      </c>
+      <c r="C89" t="s">
+        <v>243</v>
+      </c>
+      <c r="D89" t="s">
+        <v>244</v>
+      </c>
+      <c r="E89">
+        <v>6</v>
+      </c>
+      <c r="F89" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89" t="s">
+        <v>43</v>
+      </c>
+      <c r="H89" t="s">
+        <v>154</v>
+      </c>
+      <c r="I89">
+        <v>2800</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89" t="s">
+        <v>40</v>
+      </c>
+      <c r="N89" s="1">
+        <v>45854</v>
+      </c>
+      <c r="O89" s="1">
+        <v>46218</v>
+      </c>
+      <c r="P89" s="1">
+        <v>45943</v>
+      </c>
+      <c r="S89" s="1">
+        <v>48602</v>
+      </c>
+      <c r="T89" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>6460</v>
+      </c>
+      <c r="C90" t="s">
+        <v>245</v>
+      </c>
+      <c r="D90" t="s">
+        <v>246</v>
+      </c>
+      <c r="E90">
+        <v>6</v>
+      </c>
+      <c r="F90" t="s">
+        <v>32</v>
+      </c>
+      <c r="G90" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90" t="s">
+        <v>154</v>
+      </c>
+      <c r="I90">
+        <v>2800</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>23</v>
+      </c>
+      <c r="M90" t="s">
+        <v>40</v>
+      </c>
+      <c r="N90" s="1">
+        <v>45854</v>
+      </c>
+      <c r="O90" s="1">
+        <v>46218</v>
+      </c>
+      <c r="P90" s="1">
+        <v>45943</v>
+      </c>
+      <c r="T90" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>6587</v>
+      </c>
+      <c r="C91" t="s">
+        <v>247</v>
+      </c>
+      <c r="D91" t="s">
+        <v>248</v>
+      </c>
+      <c r="E91">
+        <v>6</v>
+      </c>
+      <c r="F91" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" t="s">
+        <v>38</v>
+      </c>
+      <c r="H91" t="s">
+        <v>154</v>
+      </c>
+      <c r="I91">
+        <v>2800</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91" t="s">
+        <v>40</v>
+      </c>
+      <c r="N91" s="1">
+        <v>45874</v>
+      </c>
+      <c r="O91" s="1">
+        <v>46238</v>
+      </c>
+      <c r="P91" s="1">
+        <v>45963</v>
+      </c>
+      <c r="T91" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>6674</v>
+      </c>
+      <c r="C92" t="s">
+        <v>249</v>
+      </c>
+      <c r="D92" t="s">
+        <v>250</v>
+      </c>
+      <c r="E92">
+        <v>5</v>
+      </c>
+      <c r="F92" t="s">
+        <v>37</v>
+      </c>
+      <c r="G92" t="s">
+        <v>38</v>
+      </c>
+      <c r="H92" t="s">
+        <v>251</v>
+      </c>
+      <c r="I92">
+        <v>2800</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>23</v>
+      </c>
+      <c r="M92" t="s">
+        <v>40</v>
+      </c>
+      <c r="N92" s="1">
+        <v>45992</v>
+      </c>
+      <c r="P92" s="1">
+        <v>45991</v>
+      </c>
+      <c r="T92" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7648</v>
+      </c>
+      <c r="C93" t="s">
+        <v>252</v>
+      </c>
+      <c r="D93" t="s">
+        <v>253</v>
+      </c>
+      <c r="E93">
+        <v>6</v>
+      </c>
+      <c r="F93" t="s">
+        <v>46</v>
+      </c>
+      <c r="G93" t="s">
+        <v>153</v>
+      </c>
+      <c r="H93" t="s">
+        <v>154</v>
+      </c>
+      <c r="I93">
+        <v>2800</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>23</v>
+      </c>
+      <c r="M93" t="s">
+        <v>40</v>
+      </c>
+      <c r="N93" s="1">
+        <v>46244</v>
+      </c>
+      <c r="P93" s="1">
+        <v>46243</v>
+      </c>
+      <c r="R93" s="1">
+        <v>46113</v>
+      </c>
+      <c r="T93" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>8008</v>
+      </c>
+      <c r="C94" t="s">
+        <v>254</v>
+      </c>
+      <c r="D94" t="s">
+        <v>255</v>
+      </c>
+      <c r="E94">
+        <v>6</v>
+      </c>
+      <c r="F94" t="s">
+        <v>32</v>
+      </c>
+      <c r="G94" t="s">
+        <v>43</v>
+      </c>
+      <c r="H94" t="s">
+        <v>154</v>
+      </c>
+      <c r="I94">
+        <v>2800</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94" t="s">
+        <v>40</v>
+      </c>
+      <c r="N94" s="1">
+        <v>46305</v>
+      </c>
+      <c r="R94" s="1">
+        <v>46377</v>
+      </c>
+      <c r="T94" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7277</v>
+      </c>
+      <c r="C95" t="s">
+        <v>256</v>
+      </c>
+      <c r="D95" t="s">
+        <v>257</v>
+      </c>
+      <c r="E95">
+        <v>6</v>
+      </c>
+      <c r="F95" t="s">
+        <v>37</v>
+      </c>
+      <c r="G95" t="s">
+        <v>38</v>
+      </c>
+      <c r="H95" t="s">
+        <v>154</v>
+      </c>
+      <c r="I95">
+        <v>2800</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" t="s">
+        <v>40</v>
+      </c>
+      <c r="N95" s="1">
+        <v>46143</v>
+      </c>
+      <c r="O95" s="1">
+        <v>46507</v>
+      </c>
+      <c r="P95" s="1">
+        <v>46232</v>
+      </c>
+      <c r="T95" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7278</v>
+      </c>
+      <c r="C96" t="s">
+        <v>258</v>
+      </c>
+      <c r="D96" t="s">
+        <v>259</v>
+      </c>
+      <c r="E96">
+        <v>6</v>
+      </c>
+      <c r="F96" t="s">
+        <v>37</v>
+      </c>
+      <c r="G96" t="s">
+        <v>38</v>
+      </c>
+      <c r="H96" t="s">
+        <v>154</v>
+      </c>
+      <c r="I96">
+        <v>2800</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
+        <v>23</v>
+      </c>
+      <c r="M96" t="s">
+        <v>40</v>
+      </c>
+      <c r="N96" s="1">
+        <v>46143</v>
+      </c>
+      <c r="O96" s="1">
+        <v>46507</v>
+      </c>
+      <c r="P96" s="1">
+        <v>46232</v>
+      </c>
+      <c r="T96" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7286</v>
+      </c>
+      <c r="C97" t="s">
+        <v>260</v>
+      </c>
+      <c r="D97" t="s">
+        <v>261</v>
+      </c>
+      <c r="E97">
+        <v>6</v>
+      </c>
+      <c r="F97" t="s">
+        <v>32</v>
+      </c>
+      <c r="G97" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" t="s">
+        <v>154</v>
+      </c>
+      <c r="I97">
+        <v>2800</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>23</v>
+      </c>
+      <c r="M97" t="s">
+        <v>40</v>
+      </c>
+      <c r="N97" s="1">
+        <v>46219</v>
+      </c>
+      <c r="P97" s="1">
+        <v>46218</v>
+      </c>
+      <c r="T97" t="s">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/samples/HR_Current.xlsx
+++ b/data/samples/HR_Current.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{276C00FB-54C1-44EA-9C14-1FF62F03E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE59BF3D-B369-4221-9711-25B1B4595947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{B35A5613-5B32-42A3-89F3-C94ABABE9032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B019D51-4B28-4BB0-9280-ADDE7A7D60F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,6 +93,363 @@
     <t>Location Arabic Name</t>
   </si>
   <si>
+    <t>Naim Howlader</t>
+  </si>
+  <si>
+    <t>نعيم حولادر</t>
+  </si>
+  <si>
+    <t>فندق ميسان روتانا المسك</t>
+  </si>
+  <si>
+    <t>الإشراف الداخلي - فندق ميسان روتانا المسك</t>
+  </si>
+  <si>
+    <t>Houseman</t>
+  </si>
+  <si>
+    <t>ذكر</t>
+  </si>
+  <si>
+    <t>بنجلاديش</t>
+  </si>
+  <si>
+    <t>المدينة - الحربي</t>
+  </si>
+  <si>
+    <t>Mohammed Yeasin Arafat</t>
+  </si>
+  <si>
+    <t>محمد ياسين عرفات</t>
+  </si>
+  <si>
+    <t>MD Sahidul Islam</t>
+  </si>
+  <si>
+    <t>مد سيدول اسلام</t>
+  </si>
+  <si>
+    <t>Estiek Hossain</t>
+  </si>
+  <si>
+    <t>اشتياق حسين</t>
+  </si>
+  <si>
+    <t>فندق ميسان التقوى</t>
+  </si>
+  <si>
+    <t>الإشراف الداخلي - فندق ميسان التقوى</t>
+  </si>
+  <si>
+    <t>Md Rahad</t>
+  </si>
+  <si>
+    <t>مد راهاد راهاد مد</t>
+  </si>
+  <si>
+    <t>ميسان رحاب المسك</t>
+  </si>
+  <si>
+    <t>حاملي الحقائب - ميسان رحاب المسك</t>
+  </si>
+  <si>
+    <t>حامل حقائب</t>
+  </si>
+  <si>
+    <t>Foaiz Ullah</t>
+  </si>
+  <si>
+    <t>فيض الله</t>
+  </si>
+  <si>
+    <t>الإشراف الداخلي - ميسان رحاب المسك</t>
+  </si>
+  <si>
+    <t>Muhammad Meer Hossion</t>
+  </si>
+  <si>
+    <t>محمد مير حوسيون</t>
+  </si>
+  <si>
+    <t>Sohel Sayedol Hoque</t>
+  </si>
+  <si>
+    <t>سهيل سعيد هوكي هوكي</t>
+  </si>
+  <si>
+    <t>Md Jamil Hossen</t>
+  </si>
+  <si>
+    <t>مد جميل حسين</t>
+  </si>
+  <si>
+    <t>فندق بلازا إن أحد</t>
+  </si>
+  <si>
+    <t>الإشراف الداخلي - فندق بلازا إن أحد</t>
+  </si>
+  <si>
+    <t>Md Sahajahan</t>
+  </si>
+  <si>
+    <t>مد شاه جهان</t>
+  </si>
+  <si>
+    <t>Zakir Hossain</t>
+  </si>
+  <si>
+    <t>زاكير اوسين</t>
+  </si>
+  <si>
+    <t>Md Rubel Miah</t>
+  </si>
+  <si>
+    <t>مد روبيل مياه</t>
+  </si>
+  <si>
+    <t>Anowar Hossain</t>
+  </si>
+  <si>
+    <t>انور اوسين</t>
+  </si>
+  <si>
+    <t>SOHAG MIA</t>
+  </si>
+  <si>
+    <t>شوهاك مد عزيز الحكيم ميا</t>
+  </si>
+  <si>
+    <t>Morshed Alam</t>
+  </si>
+  <si>
+    <t>مرشد علام</t>
+  </si>
+  <si>
+    <t>Samim Hossain</t>
+  </si>
+  <si>
+    <t>شميم اوسين</t>
+  </si>
+  <si>
+    <t>Md Hamidul Islam</t>
+  </si>
+  <si>
+    <t>مد حميد ال اسلام</t>
+  </si>
+  <si>
+    <t>Md Belal Hossen</t>
+  </si>
+  <si>
+    <t>مد حسين بلال</t>
+  </si>
+  <si>
+    <t>Md Sujib Mia</t>
+  </si>
+  <si>
+    <t>مد سوجيب مياه</t>
+  </si>
+  <si>
+    <t>Md Alamin Mia</t>
+  </si>
+  <si>
+    <t>محمد لامين ميا</t>
+  </si>
+  <si>
+    <t>Junaed Md Jamir Ali</t>
+  </si>
+  <si>
+    <t>جوند محمد جامير علي علي</t>
+  </si>
+  <si>
+    <t>Md Shakhawat Hossain</t>
+  </si>
+  <si>
+    <t>مد شخوات اوسين</t>
+  </si>
+  <si>
+    <t>Md Al Amin</t>
+  </si>
+  <si>
+    <t>مد ال أمين</t>
+  </si>
+  <si>
+    <t>Md Shakil Rana</t>
+  </si>
+  <si>
+    <t>مد شكيل رنا</t>
+  </si>
+  <si>
+    <t>Alif Hasan Rabby</t>
+  </si>
+  <si>
+    <t>اليف حسان ربي</t>
+  </si>
+  <si>
+    <t>Md Uzzal Mia</t>
+  </si>
+  <si>
+    <t>مد اوزال ميا</t>
+  </si>
+  <si>
+    <t>Mohammad Abu Tahar</t>
+  </si>
+  <si>
+    <t>محمد ابو طاهر ابو طاهر طاهر</t>
+  </si>
+  <si>
+    <t>Md Jishan</t>
+  </si>
+  <si>
+    <t>مد جيشان</t>
+  </si>
+  <si>
+    <t>Faysal Pathan</t>
+  </si>
+  <si>
+    <t>فيصل باثين كاشم باتهان</t>
+  </si>
+  <si>
+    <t>Md Roman Miah</t>
+  </si>
+  <si>
+    <t>مد رومان مياه</t>
+  </si>
+  <si>
+    <t>Mohammad Monir</t>
+  </si>
+  <si>
+    <t>محمد منير</t>
+  </si>
+  <si>
+    <t>MD Shahidul Islam</t>
+  </si>
+  <si>
+    <t>مد شهيد الاسلام</t>
+  </si>
+  <si>
+    <t>المدينة - موارد</t>
+  </si>
+  <si>
+    <t>MOHAMMAD HUMAYUN</t>
+  </si>
+  <si>
+    <t>محمد هومايون منصور علي</t>
+  </si>
+  <si>
+    <t>Asst. Catering Manager</t>
+  </si>
+  <si>
+    <t>MD Somon Miah</t>
+  </si>
+  <si>
+    <t>مد شمون مياه</t>
+  </si>
+  <si>
+    <t>المدينة - جبل احد</t>
+  </si>
+  <si>
+    <t>AHAMMAD ALI MAFIJ UDDIN</t>
+  </si>
+  <si>
+    <t>احمد علي مفيض دين</t>
+  </si>
+  <si>
+    <t>SAFIULLAH ABDUL KADIR</t>
+  </si>
+  <si>
+    <t>صفي الله عبد ال قادر</t>
+  </si>
+  <si>
+    <t>Sakawat Hossen</t>
+  </si>
+  <si>
+    <t>سخاوات اوسين</t>
+  </si>
+  <si>
+    <t>MD Mizanur Rahman</t>
+  </si>
+  <si>
+    <t>مد ميزان نور رحمن</t>
+  </si>
+  <si>
+    <t>Rakib Hossain</t>
+  </si>
+  <si>
+    <t>رقيب حسين</t>
+  </si>
+  <si>
+    <t>MD Faruq</t>
+  </si>
+  <si>
+    <t>مد قاروق</t>
+  </si>
+  <si>
+    <t>Ahmadulla Mamun</t>
+  </si>
+  <si>
+    <t>أحمد الله مامون</t>
+  </si>
+  <si>
+    <t>Mohammad Jihad Hossain</t>
+  </si>
+  <si>
+    <t>محمد جهاد حسين</t>
+  </si>
+  <si>
+    <t>Alamin Abo Taher</t>
+  </si>
+  <si>
+    <t>الامين ابو الطاهر</t>
+  </si>
+  <si>
+    <t>MD Nobibur Rahman</t>
+  </si>
+  <si>
+    <t>مد نوبيب ال رحمن</t>
+  </si>
+  <si>
+    <t>MD Joynal Mia</t>
+  </si>
+  <si>
+    <t>مد جونيال ميا</t>
+  </si>
+  <si>
+    <t>MD Ahnaf</t>
+  </si>
+  <si>
+    <t>مد احناف</t>
+  </si>
+  <si>
+    <t>حاملي الحقائب - فندق ميسان روتانا المسك</t>
+  </si>
+  <si>
+    <t>المدينة - ارض النظافة</t>
+  </si>
+  <si>
+    <t>Shahriar Nawas</t>
+  </si>
+  <si>
+    <t>شهريار نواز</t>
+  </si>
+  <si>
+    <t>Sarif Hannan</t>
+  </si>
+  <si>
+    <t>شريف حنان</t>
+  </si>
+  <si>
+    <t>MD Shakayet Turaz</t>
+  </si>
+  <si>
+    <t>مد شاكيت توراز</t>
+  </si>
+  <si>
+    <t>Saif Al Mohamed Islam Islam</t>
+  </si>
+  <si>
+    <t>سيف ال محمد اسلام اسلام</t>
+  </si>
+  <si>
     <t>Mohamed Shabaan Ragheb Mohamed</t>
   </si>
   <si>
@@ -105,9 +462,6 @@
     <t>مدير تشغيل مجموعة فنادق</t>
   </si>
   <si>
-    <t>ذكر</t>
-  </si>
-  <si>
     <t>مصرى</t>
   </si>
   <si>
@@ -126,15 +480,24 @@
     <t>السعودية</t>
   </si>
   <si>
+    <t>Abdul Aziz Gehaieh Redaiman Al Marwani</t>
+  </si>
+  <si>
+    <t>عبد العزيز حجيج رضيمان المرواني</t>
+  </si>
+  <si>
+    <t>السلامة - فندق بلازا إن أحد</t>
+  </si>
+  <si>
+    <t>موظف سلامة</t>
+  </si>
+  <si>
     <t>Mohmmed Hmoud Mohammed Alhaidari</t>
   </si>
   <si>
     <t>محمد حمود محمد الحيدري</t>
   </si>
   <si>
-    <t>فندق بلازا إن أحد</t>
-  </si>
-  <si>
     <t>المكاتب الأمامية - فندق بلازا إن أحد</t>
   </si>
   <si>
@@ -147,40 +510,82 @@
     <t>شاه علام</t>
   </si>
   <si>
-    <t>ميسان رحاب المسك</t>
-  </si>
-  <si>
-    <t>الإشراف الداخلي - ميسان رحاب المسك</t>
-  </si>
-  <si>
     <t>مشرف قسم الاشراف</t>
   </si>
   <si>
-    <t>بنجلاديش</t>
-  </si>
-  <si>
     <t>Aftab Ben Yousuf</t>
   </si>
   <si>
     <t>افتاب بن يوسف</t>
   </si>
   <si>
-    <t>الإشراف الداخلي - فندق بلازا إن أحد</t>
-  </si>
-  <si>
     <t>Jawad Meshal Radhiman Almarwani</t>
   </si>
   <si>
     <t>جواد مشعل رضيمان المرواني</t>
   </si>
   <si>
-    <t>فندق ميسان روتانا المسك</t>
-  </si>
-  <si>
     <t>السلامة - فندق ميسان روتانا المسك</t>
   </si>
   <si>
-    <t>موظف سلامة</t>
+    <t>Bandar Suhayyan Salm Al Harbi</t>
+  </si>
+  <si>
+    <t>بندر سهيان سالم الحربي</t>
+  </si>
+  <si>
+    <t>Shamim Yeakub Ali A</t>
+  </si>
+  <si>
+    <t>شميم يعقوب علي أ</t>
+  </si>
+  <si>
+    <t>كبير مشرفي الاشراف</t>
+  </si>
+  <si>
+    <t>Karim Moustafa Abd Elfattah Ali</t>
+  </si>
+  <si>
+    <t>كريم مصطفى عبد الفتاح علي</t>
+  </si>
+  <si>
+    <t>مساعد تشغيل</t>
+  </si>
+  <si>
+    <t>Najla Abdullah Eayid Aljabiri Alharbi</t>
+  </si>
+  <si>
+    <t>نجلاء عبدالله عائض الجابري الحربي</t>
+  </si>
+  <si>
+    <t>المكاتب الأمامية - ميسان رحاب المسك</t>
+  </si>
+  <si>
+    <t>أنثى</t>
+  </si>
+  <si>
+    <t>Sami Saad Sahyan AlAwfi AlHarbi</t>
+  </si>
+  <si>
+    <t>سامي سعد سهيان العوفي الحربي</t>
+  </si>
+  <si>
+    <t>السلامة - فندق ميسان التقوى</t>
+  </si>
+  <si>
+    <t>مشرف امن وسلامة</t>
+  </si>
+  <si>
+    <t>Omar Saud Dawihia Alealwi Aloufi</t>
+  </si>
+  <si>
+    <t>عمر سعود ضويحي العلوي العوفي</t>
+  </si>
+  <si>
+    <t>الأمن  - فندق ميسان التقوى</t>
+  </si>
+  <si>
+    <t>حارس أمن</t>
   </si>
   <si>
     <t>Basam Musleh Maghly Aljabry</t>
@@ -198,12 +603,15 @@
     <t>صلاح موسى مسلم الصاوي</t>
   </si>
   <si>
-    <t>المكاتب الأمامية - ميسان رحاب المسك</t>
-  </si>
-  <si>
     <t>موظف استقبال</t>
   </si>
   <si>
+    <t>Nor Hoshan Nurul Islam</t>
+  </si>
+  <si>
+    <t>نور هوشان اسلام</t>
+  </si>
+  <si>
     <t>Mahmoud Ibrahim Alhedram Alshanqiti</t>
   </si>
   <si>
@@ -234,12 +642,6 @@
     <t>مهند منصور شافي العنزي</t>
   </si>
   <si>
-    <t>فندق ميسان التقوى</t>
-  </si>
-  <si>
-    <t>السلامة - فندق ميسان التقوى</t>
-  </si>
-  <si>
     <t>Abdullah Faisal Mansur Alrashidi</t>
   </si>
   <si>
@@ -270,9 +672,6 @@
     <t>الأمن  - فندق ميسان روتانا المسك</t>
   </si>
   <si>
-    <t>حارس أمن</t>
-  </si>
-  <si>
     <t>Abdullah Altayeb Mohammed Abdulqader</t>
   </si>
   <si>
@@ -318,9 +717,6 @@
     <t>تسنيم خالد عبدالقادر جاري</t>
   </si>
   <si>
-    <t>أنثى</t>
-  </si>
-  <si>
     <t>Miad Meshal Aldhahri</t>
   </si>
   <si>
@@ -420,406 +816,10 @@
     <t>ريان حاتم المحمدي</t>
   </si>
   <si>
-    <t>الأمن  - فندق ميسان التقوى</t>
-  </si>
-  <si>
     <t>Zeeb Ahmed Mzyby Awagy</t>
   </si>
   <si>
     <t>ذيب أحمد مذيبي عواجي</t>
-  </si>
-  <si>
-    <t>Nor Hoshan Nurul Islam</t>
-  </si>
-  <si>
-    <t>نور هوشان اسلام</t>
-  </si>
-  <si>
-    <t>Omar Saud Dawihia Alealwi Aloufi</t>
-  </si>
-  <si>
-    <t>عمر سعود ضويحي العلوي العوفي</t>
-  </si>
-  <si>
-    <t>Sami Saad Sahyan AlAwfi AlHarbi</t>
-  </si>
-  <si>
-    <t>سامي سعد سهيان العوفي الحربي</t>
-  </si>
-  <si>
-    <t>مشرف امن وسلامة</t>
-  </si>
-  <si>
-    <t>Najla Abdullah Eayid Aljabiri Alharbi</t>
-  </si>
-  <si>
-    <t>نجلاء عبدالله عائض الجابري الحربي</t>
-  </si>
-  <si>
-    <t>Karim Moustafa Abd Elfattah Ali</t>
-  </si>
-  <si>
-    <t>كريم مصطفى عبد الفتاح علي</t>
-  </si>
-  <si>
-    <t>مساعد تشغيل</t>
-  </si>
-  <si>
-    <t>Shamim Yeakub Ali A</t>
-  </si>
-  <si>
-    <t>شميم يعقوب علي أ</t>
-  </si>
-  <si>
-    <t>كبير مشرفي الاشراف</t>
-  </si>
-  <si>
-    <t>Bandar Suhayyan Salm Al Harbi</t>
-  </si>
-  <si>
-    <t>بندر سهيان سالم الحربي</t>
-  </si>
-  <si>
-    <t>السلامة - فندق بلازا إن أحد</t>
-  </si>
-  <si>
-    <t>Abdul Aziz Gehaieh Redaiman Al Marwani</t>
-  </si>
-  <si>
-    <t>عبد العزيز حجيج رضيمان المرواني</t>
-  </si>
-  <si>
-    <t>MD Sahidul Islam</t>
-  </si>
-  <si>
-    <t>مد سيدول اسلام</t>
-  </si>
-  <si>
-    <t>الإشراف الداخلي - فندق ميسان روتانا المسك</t>
-  </si>
-  <si>
-    <t>Houseman</t>
-  </si>
-  <si>
-    <t>المدينة - الحربي</t>
-  </si>
-  <si>
-    <t>Samim Hossain</t>
-  </si>
-  <si>
-    <t>شميم اوسين</t>
-  </si>
-  <si>
-    <t>Md Hamidul Islam</t>
-  </si>
-  <si>
-    <t>مد حميد ال اسلام</t>
-  </si>
-  <si>
-    <t>Md Belal Hossen</t>
-  </si>
-  <si>
-    <t>مد حسين بلال</t>
-  </si>
-  <si>
-    <t>Md Sujib Mia</t>
-  </si>
-  <si>
-    <t>مد سوجيب مياه</t>
-  </si>
-  <si>
-    <t>الإشراف الداخلي - فندق ميسان التقوى</t>
-  </si>
-  <si>
-    <t>Morshed Alam</t>
-  </si>
-  <si>
-    <t>مرشد علام</t>
-  </si>
-  <si>
-    <t>SOHAG MIA</t>
-  </si>
-  <si>
-    <t>شوهاك مد عزيز الحكيم ميا</t>
-  </si>
-  <si>
-    <t>Anowar Hossain</t>
-  </si>
-  <si>
-    <t>انور اوسين</t>
-  </si>
-  <si>
-    <t>Md Rubel Miah</t>
-  </si>
-  <si>
-    <t>مد روبيل مياه</t>
-  </si>
-  <si>
-    <t>حاملي الحقائب - ميسان رحاب المسك</t>
-  </si>
-  <si>
-    <t>حامل حقائب</t>
-  </si>
-  <si>
-    <t>Zakir Hossain</t>
-  </si>
-  <si>
-    <t>زاكير اوسين</t>
-  </si>
-  <si>
-    <t>Md Sahajahan</t>
-  </si>
-  <si>
-    <t>مد شاه جهان</t>
-  </si>
-  <si>
-    <t>Md Jamil Hossen</t>
-  </si>
-  <si>
-    <t>مد جميل حسين</t>
-  </si>
-  <si>
-    <t>Sohel Sayedol Hoque</t>
-  </si>
-  <si>
-    <t>سهيل سعيد هوكي هوكي</t>
-  </si>
-  <si>
-    <t>Muhammad Meer Hossion</t>
-  </si>
-  <si>
-    <t>محمد مير حوسيون</t>
-  </si>
-  <si>
-    <t>Foaiz Ullah</t>
-  </si>
-  <si>
-    <t>فيض الله</t>
-  </si>
-  <si>
-    <t>Md Roman Miah</t>
-  </si>
-  <si>
-    <t>مد رومان مياه</t>
-  </si>
-  <si>
-    <t>Md Rahad</t>
-  </si>
-  <si>
-    <t>مد راهاد راهاد مد</t>
-  </si>
-  <si>
-    <t>MD Shahidul Islam</t>
-  </si>
-  <si>
-    <t>مد شهيد الاسلام</t>
-  </si>
-  <si>
-    <t>المدينة - موارد</t>
-  </si>
-  <si>
-    <t>Estiek Hossain</t>
-  </si>
-  <si>
-    <t>اشتياق حسين</t>
-  </si>
-  <si>
-    <t>MD Somon Miah</t>
-  </si>
-  <si>
-    <t>مد شمون مياه</t>
-  </si>
-  <si>
-    <t>المدينة - جبل احد</t>
-  </si>
-  <si>
-    <t>Mohammed Yeasin Arafat</t>
-  </si>
-  <si>
-    <t>محمد ياسين عرفات</t>
-  </si>
-  <si>
-    <t>Naim Howlader</t>
-  </si>
-  <si>
-    <t>نعيم حولادر</t>
-  </si>
-  <si>
-    <t>Md Alamin Mia</t>
-  </si>
-  <si>
-    <t>محمد لامين ميا</t>
-  </si>
-  <si>
-    <t>MD Mizanur Rahman</t>
-  </si>
-  <si>
-    <t>مد ميزان نور رحمن</t>
-  </si>
-  <si>
-    <t>Rakib Hossain</t>
-  </si>
-  <si>
-    <t>رقيب حسين</t>
-  </si>
-  <si>
-    <t>MD Faruq</t>
-  </si>
-  <si>
-    <t>مد قاروق</t>
-  </si>
-  <si>
-    <t>Ahmadulla Mamun</t>
-  </si>
-  <si>
-    <t>أحمد الله مامون</t>
-  </si>
-  <si>
-    <t>Mohammad Jihad Hossain</t>
-  </si>
-  <si>
-    <t>محمد جهاد حسين</t>
-  </si>
-  <si>
-    <t>Alamin Abo Taher</t>
-  </si>
-  <si>
-    <t>الامين ابو الطاهر</t>
-  </si>
-  <si>
-    <t>MD Nobibur Rahman</t>
-  </si>
-  <si>
-    <t>مد نوبيب ال رحمن</t>
-  </si>
-  <si>
-    <t>MD Joynal Mia</t>
-  </si>
-  <si>
-    <t>مد جونيال ميا</t>
-  </si>
-  <si>
-    <t>MD Ahnaf</t>
-  </si>
-  <si>
-    <t>مد احناف</t>
-  </si>
-  <si>
-    <t>حاملي الحقائب - فندق ميسان روتانا المسك</t>
-  </si>
-  <si>
-    <t>المدينة - ارض النظافة</t>
-  </si>
-  <si>
-    <t>Shahriar Nawas</t>
-  </si>
-  <si>
-    <t>شهريار نواز</t>
-  </si>
-  <si>
-    <t>Sarif Hannan</t>
-  </si>
-  <si>
-    <t>شريف حنان</t>
-  </si>
-  <si>
-    <t>Junaed Md Jamir Ali</t>
-  </si>
-  <si>
-    <t>جوند محمد جامير علي علي</t>
-  </si>
-  <si>
-    <t>Md Shakhawat Hossain</t>
-  </si>
-  <si>
-    <t>مد شخوات اوسين</t>
-  </si>
-  <si>
-    <t>Md Al Amin</t>
-  </si>
-  <si>
-    <t>مد ال أمين</t>
-  </si>
-  <si>
-    <t>Md Shakil Rana</t>
-  </si>
-  <si>
-    <t>مد شكيل رنا</t>
-  </si>
-  <si>
-    <t>Alif Hasan Rabby</t>
-  </si>
-  <si>
-    <t>اليف حسان ربي</t>
-  </si>
-  <si>
-    <t>Md Uzzal Mia</t>
-  </si>
-  <si>
-    <t>مد اوزال ميا</t>
-  </si>
-  <si>
-    <t>Mohammad Abu Tahar</t>
-  </si>
-  <si>
-    <t>محمد ابو طاهر ابو طاهر طاهر</t>
-  </si>
-  <si>
-    <t>Md Jishan</t>
-  </si>
-  <si>
-    <t>مد جيشان</t>
-  </si>
-  <si>
-    <t>Faysal Pathan</t>
-  </si>
-  <si>
-    <t>فيصل باثين كاشم باتهان</t>
-  </si>
-  <si>
-    <t>Mohammad Monir</t>
-  </si>
-  <si>
-    <t>محمد منير</t>
-  </si>
-  <si>
-    <t>MOHAMMAD HUMAYUN</t>
-  </si>
-  <si>
-    <t>محمد هومايون منصور علي</t>
-  </si>
-  <si>
-    <t>Asst. Catering Manager</t>
-  </si>
-  <si>
-    <t>MD Shakayet Turaz</t>
-  </si>
-  <si>
-    <t>مد شاكيت توراز</t>
-  </si>
-  <si>
-    <t>Saif Al Mohamed Islam Islam</t>
-  </si>
-  <si>
-    <t>سيف ال محمد اسلام اسلام</t>
-  </si>
-  <si>
-    <t>AHAMMAD ALI MAFIJ UDDIN</t>
-  </si>
-  <si>
-    <t>احمد علي مفيض دين</t>
-  </si>
-  <si>
-    <t>SAFIULLAH ABDUL KADIR</t>
-  </si>
-  <si>
-    <t>صفي الله عبد ال قادر</t>
-  </si>
-  <si>
-    <t>Sakawat Hossen</t>
-  </si>
-  <si>
-    <t>سخاوات اوسين</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883B3F3C-5A92-453D-9638-D2640977E06C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41636F6B-6EE6-41FD-897C-6EC9C9FB3CDE}">
   <dimension ref="A1:T97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1240,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1005</v>
+        <v>2649</v>
       </c>
       <c r="C2" t="s">
         <v>19</v>
@@ -1249,49 +1249,43 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>14000</v>
+        <v>2800</v>
       </c>
       <c r="J2">
-        <v>32.812403330000002</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1">
-        <v>44639</v>
-      </c>
-      <c r="O2" s="1">
-        <v>46598</v>
+        <v>46244</v>
       </c>
       <c r="P2" s="1">
-        <v>44729</v>
+        <v>46243</v>
       </c>
       <c r="R2" s="1">
-        <v>46574</v>
-      </c>
-      <c r="S2" s="1">
-        <v>48849</v>
+        <v>45729</v>
       </c>
       <c r="T2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -1299,49 +1293,52 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1033</v>
+        <v>2650</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>9893</v>
+        <v>2800</v>
       </c>
       <c r="J3">
-        <v>78.917263329999997</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1">
-        <v>44671</v>
+        <v>46244</v>
       </c>
       <c r="P3" s="1">
-        <v>44761</v>
+        <v>46243</v>
+      </c>
+      <c r="R3" s="1">
+        <v>46216</v>
       </c>
       <c r="T3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -1349,49 +1346,52 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1226</v>
+        <v>2651</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I4">
-        <v>5276</v>
+        <v>2800</v>
       </c>
       <c r="J4">
-        <v>24.863326669999999</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N4" s="1">
-        <v>44944</v>
+        <v>46244</v>
       </c>
       <c r="P4" s="1">
-        <v>45034</v>
+        <v>46243</v>
+      </c>
+      <c r="R4" s="1">
+        <v>46006</v>
       </c>
       <c r="T4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -1399,58 +1399,52 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1249</v>
+        <v>5128</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I5">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J5">
-        <v>19.97716333</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N5" s="1">
         <v>44808</v>
       </c>
-      <c r="O5" s="1">
-        <v>46536</v>
-      </c>
       <c r="P5" s="1">
-        <v>44986</v>
+        <v>44898</v>
       </c>
       <c r="R5" s="1">
-        <v>46583</v>
-      </c>
-      <c r="S5" s="1">
-        <v>46264</v>
+        <v>46319</v>
       </c>
       <c r="T5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -1458,58 +1452,52 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1250</v>
+        <v>5484</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J6">
-        <v>4.4636066669999996</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N6" s="1">
-        <v>44643</v>
-      </c>
-      <c r="O6" s="1">
-        <v>46509</v>
+        <v>45216</v>
       </c>
       <c r="P6" s="1">
-        <v>44821</v>
+        <v>45305</v>
       </c>
       <c r="R6" s="1">
-        <v>46613</v>
-      </c>
-      <c r="S6" s="1">
-        <v>49512</v>
+        <v>45117</v>
       </c>
       <c r="T6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -1517,49 +1505,52 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1266</v>
+        <v>5773</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I7">
-        <v>4947</v>
+        <v>2800</v>
       </c>
       <c r="J7">
-        <v>8.2329733330000003</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N7" s="1">
-        <v>45045</v>
+        <v>45485</v>
       </c>
       <c r="P7" s="1">
-        <v>45134</v>
+        <v>45574</v>
+      </c>
+      <c r="R7" s="1">
+        <v>45661</v>
       </c>
       <c r="T7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -1567,49 +1558,55 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1459</v>
+        <v>5830</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I8">
-        <v>4727</v>
+        <v>2800</v>
       </c>
       <c r="J8">
-        <v>38.687199999999997</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N8" s="1">
-        <v>45231</v>
+        <v>45515</v>
       </c>
       <c r="P8" s="1">
-        <v>45320</v>
+        <v>45604</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>46323</v>
+      </c>
+      <c r="R8" s="1">
+        <v>45979</v>
       </c>
       <c r="T8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -1617,49 +1614,52 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1473</v>
+        <v>5961</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I9">
-        <v>4837</v>
+        <v>2800</v>
       </c>
       <c r="J9">
-        <v>4.9613533329999999</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N9" s="1">
-        <v>45245</v>
+        <v>45536</v>
       </c>
       <c r="P9" s="1">
-        <v>45334</v>
+        <v>45625</v>
+      </c>
+      <c r="R9" s="1">
+        <v>45783</v>
       </c>
       <c r="T9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -1667,49 +1667,55 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1860</v>
+        <v>5993</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I10">
-        <v>4617</v>
+        <v>2800</v>
       </c>
       <c r="J10">
-        <v>14.598466670000001</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N10" s="1">
-        <v>45627</v>
+        <v>45569</v>
       </c>
       <c r="P10" s="1">
-        <v>45716</v>
+        <v>45658</v>
+      </c>
+      <c r="R10" s="1">
+        <v>45652</v>
+      </c>
+      <c r="S10" s="1">
+        <v>48876</v>
       </c>
       <c r="T10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -1717,49 +1723,52 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1927</v>
+        <v>5995</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I11">
-        <v>4507</v>
+        <v>2800</v>
       </c>
       <c r="J11">
-        <v>32.867199999999997</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N11" s="1">
-        <v>45691</v>
+        <v>45583</v>
       </c>
       <c r="P11" s="1">
-        <v>45780</v>
+        <v>45672</v>
+      </c>
+      <c r="R11" s="1">
+        <v>45652</v>
       </c>
       <c r="T11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -1767,52 +1776,55 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1928</v>
+        <v>6085</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I12">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J12">
-        <v>2.51586</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N12" s="1">
-        <v>45697</v>
+        <v>45641</v>
       </c>
       <c r="P12" s="1">
-        <v>45786</v>
+        <v>45730</v>
       </c>
       <c r="R12" s="1">
-        <v>46394</v>
+        <v>46008</v>
+      </c>
+      <c r="S12" s="1">
+        <v>48099</v>
       </c>
       <c r="T12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -1820,49 +1832,55 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1935</v>
+        <v>6086</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I13">
-        <v>4507</v>
+        <v>2800</v>
       </c>
       <c r="J13">
-        <v>11.760403330000001</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N13" s="1">
-        <v>45698</v>
+        <v>45641</v>
       </c>
       <c r="P13" s="1">
-        <v>45787</v>
+        <v>45730</v>
+      </c>
+      <c r="R13" s="1">
+        <v>46794</v>
+      </c>
+      <c r="S13" s="1">
+        <v>49191</v>
       </c>
       <c r="T13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -1870,49 +1888,52 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1939</v>
+        <v>6092</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I14">
-        <v>4617</v>
+        <v>2800</v>
       </c>
       <c r="J14">
-        <v>10.136846670000001</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N14" s="1">
-        <v>45698</v>
+        <v>45637</v>
       </c>
       <c r="P14" s="1">
-        <v>45787</v>
+        <v>45726</v>
+      </c>
+      <c r="R14" s="1">
+        <v>44933</v>
       </c>
       <c r="T14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -1920,49 +1941,55 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1940</v>
+        <v>6120</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I15">
-        <v>4617</v>
+        <v>2800</v>
       </c>
       <c r="J15">
-        <v>20.63170667</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M15" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N15" s="1">
-        <v>45701</v>
+        <v>45645</v>
+      </c>
+      <c r="O15" s="1">
+        <v>46009</v>
       </c>
       <c r="P15" s="1">
-        <v>45790</v>
+        <v>45734</v>
+      </c>
+      <c r="R15" s="1">
+        <v>45698</v>
       </c>
       <c r="T15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -1970,49 +1997,55 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1941</v>
+        <v>6122</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I16">
-        <v>4617</v>
+        <v>2800</v>
       </c>
       <c r="J16">
-        <v>26.689769999999999</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N16" s="1">
-        <v>45706</v>
+        <v>45645</v>
+      </c>
+      <c r="O16" s="1">
+        <v>46009</v>
       </c>
       <c r="P16" s="1">
-        <v>45795</v>
+        <v>45734</v>
+      </c>
+      <c r="R16" s="1">
+        <v>46361</v>
       </c>
       <c r="T16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -2020,49 +2053,55 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1971</v>
+        <v>6126</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E17">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I17">
-        <v>4220</v>
+        <v>2800</v>
       </c>
       <c r="J17">
-        <v>19.018149999999999</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N17" s="1">
-        <v>45724</v>
+        <v>45645</v>
+      </c>
+      <c r="O17" s="1">
+        <v>46009</v>
       </c>
       <c r="P17" s="1">
-        <v>45813</v>
+        <v>45734</v>
+      </c>
+      <c r="R17" s="1">
+        <v>45673</v>
       </c>
       <c r="T17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -2070,49 +2109,55 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1972</v>
+        <v>6127</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I18">
-        <v>4617</v>
+        <v>2800</v>
       </c>
       <c r="J18">
-        <v>26.823643329999999</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N18" s="1">
-        <v>45721</v>
+        <v>45645</v>
+      </c>
+      <c r="O18" s="1">
+        <v>46009</v>
       </c>
       <c r="P18" s="1">
-        <v>45810</v>
+        <v>45734</v>
+      </c>
+      <c r="R18" s="1">
+        <v>45006</v>
       </c>
       <c r="T18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -2120,49 +2165,55 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2078</v>
+        <v>6129</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I19">
-        <v>4617</v>
+        <v>2800</v>
       </c>
       <c r="J19">
-        <v>16.338149999999999</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M19" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N19" s="1">
-        <v>45858</v>
+        <v>45901</v>
+      </c>
+      <c r="O19" s="1">
+        <v>46265</v>
       </c>
       <c r="P19" s="1">
-        <v>46038</v>
+        <v>45990</v>
+      </c>
+      <c r="R19" s="1">
+        <v>46250</v>
       </c>
       <c r="T19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -2170,49 +2221,58 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2298</v>
+        <v>6145</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I20">
-        <v>4287</v>
+        <v>2800</v>
       </c>
       <c r="J20">
-        <v>11.49202333</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N20" s="1">
-        <v>46026</v>
+        <v>45901</v>
+      </c>
+      <c r="O20" s="1">
+        <v>46265</v>
       </c>
       <c r="P20" s="1">
-        <v>46204</v>
+        <v>45990</v>
+      </c>
+      <c r="R20" s="1">
+        <v>45661</v>
+      </c>
+      <c r="S20" s="1">
+        <v>48992</v>
       </c>
       <c r="T20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -2220,58 +2280,55 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2350</v>
+        <v>6166</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I21">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="J21">
-        <v>29.5472</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M21" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="N21" s="1">
-        <v>45904</v>
+        <v>45658</v>
       </c>
       <c r="O21" s="1">
-        <v>46633</v>
+        <v>46022</v>
       </c>
       <c r="P21" s="1">
-        <v>45993</v>
+        <v>45747</v>
       </c>
       <c r="R21" s="1">
-        <v>46623</v>
-      </c>
-      <c r="S21" s="1">
-        <v>48850</v>
+        <v>45661</v>
       </c>
       <c r="T21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -2279,49 +2336,55 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2443</v>
+        <v>6233</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E22">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I22">
-        <v>4001</v>
+        <v>2800</v>
       </c>
       <c r="J22">
-        <v>13.37832</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M22" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N22" s="1">
-        <v>46167</v>
+        <v>45717</v>
+      </c>
+      <c r="O22" s="1">
+        <v>46081</v>
       </c>
       <c r="P22" s="1">
-        <v>46345</v>
+        <v>45806</v>
+      </c>
+      <c r="R22" s="1">
+        <v>45719</v>
       </c>
       <c r="T22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -2329,49 +2392,55 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2444</v>
+        <v>6234</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I23">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J23">
-        <v>34.0672</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="M23" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N23" s="1">
-        <v>46194</v>
+        <v>45717</v>
+      </c>
+      <c r="O23" s="1">
+        <v>46081</v>
       </c>
       <c r="P23" s="1">
-        <v>46372</v>
+        <v>45806</v>
+      </c>
+      <c r="R23" s="1">
+        <v>45746</v>
       </c>
       <c r="T23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -2379,49 +2448,55 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2445</v>
+        <v>6235</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I24">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J24">
-        <v>8.2105366669999995</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N24" s="1">
-        <v>46200</v>
+        <v>45717</v>
+      </c>
+      <c r="O24" s="1">
+        <v>46081</v>
       </c>
       <c r="P24" s="1">
-        <v>46378</v>
+        <v>45806</v>
+      </c>
+      <c r="R24" s="1">
+        <v>45718</v>
       </c>
       <c r="T24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -2429,49 +2504,55 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2447</v>
+        <v>6236</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I25">
-        <v>4001</v>
+        <v>2800</v>
       </c>
       <c r="J25">
-        <v>33.197200000000002</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N25" s="1">
-        <v>46208</v>
+        <v>45717</v>
+      </c>
+      <c r="O25" s="1">
+        <v>46081</v>
       </c>
       <c r="P25" s="1">
-        <v>46389</v>
+        <v>45806</v>
+      </c>
+      <c r="R25" s="1">
+        <v>45440</v>
       </c>
       <c r="T25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -2479,49 +2560,55 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2448</v>
+        <v>6237</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I26">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J26">
-        <v>10.65310667</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N26" s="1">
-        <v>46212</v>
+        <v>45717</v>
+      </c>
+      <c r="O26" s="1">
+        <v>46081</v>
       </c>
       <c r="P26" s="1">
-        <v>46396</v>
+        <v>45806</v>
+      </c>
+      <c r="R26" s="1">
+        <v>46089</v>
       </c>
       <c r="T26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -2529,49 +2616,52 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2449</v>
+        <v>6450</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I27">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J27">
-        <v>10.71504333</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M27" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N27" s="1">
-        <v>46211</v>
+        <v>45854</v>
+      </c>
+      <c r="O27" s="1">
+        <v>46218</v>
       </c>
       <c r="P27" s="1">
-        <v>46392</v>
+        <v>45943</v>
       </c>
       <c r="T27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -2579,49 +2669,52 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>2451</v>
+        <v>6455</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I28">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J28">
-        <v>10.65310667</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M28" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N28" s="1">
-        <v>46212</v>
+        <v>45854</v>
+      </c>
+      <c r="O28" s="1">
+        <v>46218</v>
       </c>
       <c r="P28" s="1">
-        <v>46393</v>
+        <v>45943</v>
       </c>
       <c r="T28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -2629,49 +2722,55 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>2452</v>
+        <v>6459</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E29">
         <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="H29" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I29">
-        <v>4001</v>
+        <v>2800</v>
       </c>
       <c r="J29">
-        <v>32.267200000000003</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M29" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N29" s="1">
-        <v>46223</v>
+        <v>45854</v>
+      </c>
+      <c r="O29" s="1">
+        <v>46218</v>
       </c>
       <c r="P29" s="1">
-        <v>46402</v>
+        <v>45943</v>
+      </c>
+      <c r="S29" s="1">
+        <v>48602</v>
       </c>
       <c r="T29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -2679,49 +2778,52 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>2454</v>
+        <v>6460</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="H30" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I30">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J30">
-        <v>31.587199999999999</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="M30" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N30" s="1">
-        <v>46235</v>
+        <v>45854</v>
+      </c>
+      <c r="O30" s="1">
+        <v>46218</v>
       </c>
       <c r="P30" s="1">
-        <v>46413</v>
+        <v>45943</v>
       </c>
       <c r="T30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -2729,49 +2831,55 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2463</v>
+        <v>6461</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I31">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J31">
-        <v>16.949770000000001</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M31" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N31" s="1">
-        <v>45953</v>
+        <v>45854</v>
+      </c>
+      <c r="O31" s="1">
+        <v>46189</v>
       </c>
       <c r="P31" s="1">
-        <v>46131</v>
+        <v>45943</v>
+      </c>
+      <c r="R31" s="1">
+        <v>45858</v>
       </c>
       <c r="T31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -2779,13 +2887,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2474</v>
+        <v>6587</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -2794,34 +2902,37 @@
         <v>37</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I32">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="J32">
-        <v>32.257199999999997</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M32" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N32" s="1">
+        <v>45874</v>
+      </c>
+      <c r="O32" s="1">
+        <v>46238</v>
+      </c>
+      <c r="P32" s="1">
         <v>45963</v>
       </c>
-      <c r="P32" s="1">
-        <v>46141</v>
-      </c>
       <c r="T32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -2829,49 +2940,55 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>2669</v>
+        <v>6589</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H33" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I33">
-        <v>4397</v>
+        <v>2800</v>
       </c>
       <c r="J33">
-        <v>13.167833330000001</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M33" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N33" s="1">
-        <v>45998</v>
+        <v>45874</v>
+      </c>
+      <c r="O33" s="1">
+        <v>46238</v>
       </c>
       <c r="P33" s="1">
-        <v>46176</v>
+        <v>45963</v>
+      </c>
+      <c r="S33" s="1">
+        <v>48500</v>
       </c>
       <c r="T33" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -2879,49 +2996,49 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2693</v>
+        <v>6674</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
         <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I34">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="J34">
-        <v>35.747199999999999</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M34" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N34" s="1">
-        <v>46056</v>
+        <v>45992</v>
       </c>
       <c r="P34" s="1">
-        <v>46234</v>
+        <v>45991</v>
       </c>
       <c r="T34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -2929,49 +3046,49 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>2708</v>
+        <v>6675</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E35">
         <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I35">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="J35">
-        <v>13.99768667</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N35" s="1">
-        <v>46157</v>
+        <v>46204</v>
       </c>
       <c r="P35" s="1">
-        <v>46335</v>
+        <v>46203</v>
       </c>
       <c r="T35" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -2979,49 +3096,52 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>2772</v>
+        <v>7277</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I36">
-        <v>4947</v>
+        <v>2800</v>
       </c>
       <c r="J36">
-        <v>7.4324000000000003</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M36" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N36" s="1">
-        <v>46266</v>
+        <v>46143</v>
+      </c>
+      <c r="O36" s="1">
+        <v>46507</v>
       </c>
       <c r="P36" s="1">
-        <v>46355</v>
+        <v>46232</v>
       </c>
       <c r="T36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -3029,49 +3149,52 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>2773</v>
+        <v>7278</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E37">
         <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I37">
-        <v>4001</v>
+        <v>2800</v>
       </c>
       <c r="J37">
-        <v>7.4324000000000003</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M37" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N37" s="1">
-        <v>46266</v>
+        <v>46143</v>
+      </c>
+      <c r="O37" s="1">
+        <v>46507</v>
       </c>
       <c r="P37" s="1">
-        <v>46355</v>
+        <v>46232</v>
       </c>
       <c r="T37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -3079,49 +3202,49 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>2778</v>
+        <v>7286</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E38">
         <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I38">
-        <v>4001</v>
+        <v>2800</v>
       </c>
       <c r="J38">
-        <v>7.370463333</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M38" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N38" s="1">
-        <v>46266</v>
+        <v>46219</v>
       </c>
       <c r="P38" s="1">
-        <v>46355</v>
+        <v>46218</v>
       </c>
       <c r="T38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -3129,49 +3252,49 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>2780</v>
+        <v>7287</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="H39" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I39">
-        <v>4001</v>
+        <v>2800</v>
       </c>
       <c r="J39">
-        <v>5.5743</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M39" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N39" s="1">
-        <v>46296</v>
+        <v>46223</v>
       </c>
       <c r="P39" s="1">
-        <v>46385</v>
+        <v>46222</v>
       </c>
       <c r="T39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -3179,55 +3302,49 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1512</v>
+        <v>7288</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H40" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I40">
-        <v>3250</v>
+        <v>2800</v>
       </c>
       <c r="J40">
-        <v>32.353326670000001</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M40" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N40" s="1">
-        <v>45281</v>
-      </c>
-      <c r="O40" s="1">
-        <v>46625</v>
+        <v>46219</v>
       </c>
       <c r="P40" s="1">
-        <v>45459</v>
-      </c>
-      <c r="R40" s="1">
-        <v>46569</v>
+        <v>46218</v>
       </c>
       <c r="T40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -3235,49 +3352,49 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>1438</v>
+        <v>7289</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="H41" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I41">
-        <v>4440</v>
+        <v>2800</v>
       </c>
       <c r="J41">
-        <v>3.59491</v>
+        <v>0</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M41" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N41" s="1">
-        <v>45214</v>
+        <v>46219</v>
       </c>
       <c r="P41" s="1">
-        <v>45303</v>
+        <v>46218</v>
       </c>
       <c r="T41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -3285,49 +3402,49 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>1379</v>
+        <v>7291</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="H42" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="I42">
-        <v>5167</v>
+        <v>2800</v>
       </c>
       <c r="J42">
-        <v>14.178466670000001</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M42" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N42" s="1">
-        <v>45175</v>
+        <v>46219</v>
       </c>
       <c r="P42" s="1">
-        <v>45264</v>
+        <v>46218</v>
       </c>
       <c r="T42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -3335,49 +3452,49 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>1352</v>
+        <v>7292</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G43" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="H43" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I43">
-        <v>5643</v>
+        <v>2800</v>
       </c>
       <c r="J43">
-        <v>7.2304033329999999</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="M43" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N43" s="1">
-        <v>45154</v>
+        <v>46219</v>
       </c>
       <c r="P43" s="1">
-        <v>45243</v>
+        <v>46218</v>
       </c>
       <c r="T43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -3385,55 +3502,49 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>1341</v>
+        <v>7293</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H44" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="I44">
-        <v>4500</v>
+        <v>2800</v>
       </c>
       <c r="J44">
-        <v>11.14739067</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N44" s="1">
-        <v>45143</v>
-      </c>
-      <c r="O44" s="1">
-        <v>46394</v>
+        <v>46219</v>
       </c>
       <c r="P44" s="1">
-        <v>45232</v>
-      </c>
-      <c r="R44" s="1">
-        <v>46465</v>
+        <v>46218</v>
       </c>
       <c r="T44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -3441,58 +3552,49 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>1338</v>
+        <v>7294</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D45" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
         <v>37</v>
       </c>
       <c r="G45" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H45" t="s">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="I45">
-        <v>3600</v>
+        <v>2800</v>
       </c>
       <c r="J45">
-        <v>5.4177966670000002</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M45" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N45" s="1">
-        <v>45139</v>
-      </c>
-      <c r="O45" s="1">
-        <v>46674</v>
+        <v>46219</v>
       </c>
       <c r="P45" s="1">
-        <v>45228</v>
-      </c>
-      <c r="R45" s="1">
-        <v>46372</v>
-      </c>
-      <c r="S45" s="1">
-        <v>46896</v>
+        <v>46218</v>
       </c>
       <c r="T45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -3500,49 +3602,49 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>1335</v>
+        <v>7295</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G46" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
       <c r="H46" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I46">
-        <v>4947</v>
+        <v>2800</v>
       </c>
       <c r="J46">
-        <v>15.65621333</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M46" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N46" s="1">
-        <v>45132</v>
+        <v>46219</v>
       </c>
       <c r="P46" s="1">
-        <v>45221</v>
+        <v>46218</v>
       </c>
       <c r="T46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -3550,49 +3652,52 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>1092</v>
+        <v>7300</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="H47" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I47">
-        <v>4947</v>
+        <v>2800</v>
       </c>
       <c r="J47">
-        <v>7.1691000000000003</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M47" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N47" s="1">
-        <v>44901</v>
+        <v>46218</v>
+      </c>
+      <c r="O47" s="1">
+        <v>46582</v>
       </c>
       <c r="P47" s="1">
-        <v>44991</v>
+        <v>46307</v>
       </c>
       <c r="T47" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -3600,25 +3705,25 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>2651</v>
+        <v>7301</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="E48">
         <v>6</v>
       </c>
       <c r="F48" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="H48" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="I48">
         <v>2800</v>
@@ -3630,22 +3735,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M48" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N48" s="1">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="P48" s="1">
-        <v>46243</v>
-      </c>
-      <c r="R48" s="1">
-        <v>46006</v>
+        <v>46217</v>
       </c>
       <c r="T48" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -3653,25 +3755,25 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>6126</v>
+        <v>7302</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="E49">
         <v>6</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="H49" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="I49">
         <v>2800</v>
@@ -3683,25 +3785,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N49" s="1">
-        <v>45645</v>
-      </c>
-      <c r="O49" s="1">
-        <v>46009</v>
+        <v>46218</v>
       </c>
       <c r="P49" s="1">
-        <v>45734</v>
-      </c>
-      <c r="R49" s="1">
-        <v>45673</v>
+        <v>46217</v>
       </c>
       <c r="T49" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -3709,25 +3805,25 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>6127</v>
+        <v>7648</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E50">
         <v>6</v>
       </c>
       <c r="F50" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H50" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="I50">
         <v>2800</v>
@@ -3739,25 +3835,22 @@
         <v>0</v>
       </c>
       <c r="L50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M50" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N50" s="1">
-        <v>45645</v>
-      </c>
-      <c r="O50" s="1">
-        <v>46009</v>
+        <v>46244</v>
       </c>
       <c r="P50" s="1">
-        <v>45734</v>
+        <v>46243</v>
       </c>
       <c r="R50" s="1">
-        <v>45006</v>
+        <v>46113</v>
       </c>
       <c r="T50" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -3765,25 +3858,25 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>6129</v>
+        <v>8008</v>
       </c>
       <c r="C51" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G51" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="I51">
         <v>2800</v>
@@ -3795,25 +3888,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M51" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N51" s="1">
-        <v>45901</v>
-      </c>
-      <c r="O51" s="1">
-        <v>46265</v>
-      </c>
-      <c r="P51" s="1">
-        <v>45990</v>
+        <v>46305</v>
       </c>
       <c r="R51" s="1">
-        <v>46250</v>
+        <v>46377</v>
       </c>
       <c r="T51" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -3821,58 +3908,58 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>6145</v>
+        <v>1005</v>
       </c>
       <c r="C52" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="D52" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="E52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="G52" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="H52" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I52">
-        <v>2800</v>
+        <v>14000</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>7.7370000000000001</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M52" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="N52" s="1">
-        <v>45901</v>
+        <v>44639</v>
       </c>
       <c r="O52" s="1">
-        <v>46265</v>
+        <v>46598</v>
       </c>
       <c r="P52" s="1">
-        <v>45990</v>
+        <v>44729</v>
       </c>
       <c r="R52" s="1">
-        <v>45661</v>
+        <v>46574</v>
       </c>
       <c r="S52" s="1">
-        <v>48992</v>
+        <v>48849</v>
       </c>
       <c r="T52" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -3880,55 +3967,49 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>6122</v>
+        <v>1033</v>
       </c>
       <c r="C53" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="G53" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="H53" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I53">
-        <v>2800</v>
+        <v>9893</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>27.737856669999999</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N53" s="1">
-        <v>45645</v>
-      </c>
-      <c r="O53" s="1">
-        <v>46009</v>
+        <v>44671</v>
       </c>
       <c r="P53" s="1">
-        <v>45734</v>
-      </c>
-      <c r="R53" s="1">
-        <v>46361</v>
+        <v>44761</v>
       </c>
       <c r="T53" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -3936,55 +4017,49 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>6120</v>
+        <v>1092</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="D54" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F54" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G54" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="H54" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I54">
-        <v>2800</v>
+        <v>4947</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>7.1691000000000003</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M54" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N54" s="1">
-        <v>45645</v>
-      </c>
-      <c r="O54" s="1">
-        <v>46009</v>
+        <v>44901</v>
       </c>
       <c r="P54" s="1">
-        <v>45734</v>
-      </c>
-      <c r="R54" s="1">
-        <v>45698</v>
+        <v>44991</v>
       </c>
       <c r="T54" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -3992,55 +4067,49 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>6092</v>
+        <v>1226</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="D55" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G55" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="H55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I55">
-        <v>2800</v>
+        <v>5276</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>24.863326669999999</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M55" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N55" s="1">
-        <v>45637</v>
-      </c>
-      <c r="O55" s="1">
-        <v>46001</v>
+        <v>44944</v>
       </c>
       <c r="P55" s="1">
-        <v>45726</v>
-      </c>
-      <c r="R55" s="1">
-        <v>44933</v>
+        <v>45034</v>
       </c>
       <c r="T55" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -4048,58 +4117,58 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>6086</v>
+        <v>1249</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D56" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" t="s">
         <v>37</v>
       </c>
       <c r="G56" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="H56" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="I56">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>19.97716333</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M56" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N56" s="1">
-        <v>45641</v>
+        <v>44808</v>
       </c>
       <c r="O56" s="1">
-        <v>46005</v>
+        <v>46536</v>
       </c>
       <c r="P56" s="1">
-        <v>45730</v>
+        <v>44986</v>
       </c>
       <c r="R56" s="1">
-        <v>46794</v>
+        <v>46583</v>
       </c>
       <c r="S56" s="1">
-        <v>49191</v>
+        <v>46264</v>
       </c>
       <c r="T56" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -4107,58 +4176,58 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>6085</v>
+        <v>1250</v>
       </c>
       <c r="C57" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D57" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G57" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="H57" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="I57">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>4.4636066669999996</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M57" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N57" s="1">
-        <v>45641</v>
+        <v>44643</v>
       </c>
       <c r="O57" s="1">
-        <v>46005</v>
+        <v>46509</v>
       </c>
       <c r="P57" s="1">
-        <v>45730</v>
+        <v>44821</v>
       </c>
       <c r="R57" s="1">
-        <v>46008</v>
+        <v>46613</v>
       </c>
       <c r="S57" s="1">
-        <v>48099</v>
+        <v>49512</v>
       </c>
       <c r="T57" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -4166,55 +4235,49 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>5995</v>
+        <v>1266</v>
       </c>
       <c r="C58" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="D58" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G58" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="H58" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I58">
-        <v>2800</v>
+        <v>4947</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>8.2329733330000003</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M58" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N58" s="1">
-        <v>45583</v>
-      </c>
-      <c r="O58" s="1">
-        <v>45947</v>
+        <v>45045</v>
       </c>
       <c r="P58" s="1">
-        <v>45672</v>
-      </c>
-      <c r="R58" s="1">
-        <v>45652</v>
+        <v>45134</v>
       </c>
       <c r="T58" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -4222,58 +4285,49 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>5993</v>
+        <v>1335</v>
       </c>
       <c r="C59" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D59" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="G59" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="H59" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I59">
-        <v>2800</v>
+        <v>4947</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>15.65621333</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M59" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N59" s="1">
-        <v>45569</v>
-      </c>
-      <c r="O59" s="1">
-        <v>45933</v>
+        <v>45132</v>
       </c>
       <c r="P59" s="1">
-        <v>45658</v>
-      </c>
-      <c r="R59" s="1">
-        <v>45652</v>
-      </c>
-      <c r="S59" s="1">
-        <v>48876</v>
+        <v>45221</v>
       </c>
       <c r="T59" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -4281,55 +4335,58 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>5961</v>
+        <v>1338</v>
       </c>
       <c r="C60" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D60" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" t="s">
         <v>37</v>
       </c>
       <c r="G60" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H60" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="I60">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>5.4177966670000002</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M60" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N60" s="1">
-        <v>45536</v>
+        <v>45139</v>
       </c>
       <c r="O60" s="1">
-        <v>45900</v>
+        <v>46674</v>
       </c>
       <c r="P60" s="1">
-        <v>45625</v>
+        <v>45228</v>
       </c>
       <c r="R60" s="1">
-        <v>45783</v>
+        <v>46372</v>
+      </c>
+      <c r="S60" s="1">
+        <v>46896</v>
       </c>
       <c r="T60" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.25">
@@ -4337,58 +4394,55 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>5830</v>
+        <v>1341</v>
       </c>
       <c r="C61" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D61" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="E61">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="G61" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="H61" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I61">
-        <v>2800</v>
+        <v>4500</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>11.14739067</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="N61" s="1">
-        <v>45515</v>
+        <v>45143</v>
       </c>
       <c r="O61" s="1">
-        <v>45879</v>
+        <v>46394</v>
       </c>
       <c r="P61" s="1">
-        <v>45604</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>46323</v>
+        <v>45232</v>
       </c>
       <c r="R61" s="1">
-        <v>45979</v>
+        <v>46465</v>
       </c>
       <c r="T61" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -4396,55 +4450,49 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5773</v>
+        <v>1352</v>
       </c>
       <c r="C62" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F62" t="s">
         <v>37</v>
       </c>
       <c r="G62" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
       <c r="H62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I62">
-        <v>2800</v>
+        <v>5643</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>7.2304033329999999</v>
       </c>
       <c r="K62">
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="M62" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N62" s="1">
-        <v>45485</v>
-      </c>
-      <c r="O62" s="1">
-        <v>45849</v>
+        <v>45154</v>
       </c>
       <c r="P62" s="1">
-        <v>45574</v>
-      </c>
-      <c r="R62" s="1">
-        <v>45661</v>
+        <v>45243</v>
       </c>
       <c r="T62" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.25">
@@ -4452,55 +4500,49 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>6461</v>
+        <v>1379</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D63" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>43</v>
+        <v>178</v>
       </c>
       <c r="H63" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="I63">
-        <v>2800</v>
+        <v>5167</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>14.178466670000001</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M63" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N63" s="1">
-        <v>45854</v>
-      </c>
-      <c r="O63" s="1">
-        <v>46189</v>
+        <v>45175</v>
       </c>
       <c r="P63" s="1">
-        <v>45943</v>
-      </c>
-      <c r="R63" s="1">
-        <v>45858</v>
+        <v>45264</v>
       </c>
       <c r="T63" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.25">
@@ -4508,55 +4550,49 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>5484</v>
+        <v>1438</v>
       </c>
       <c r="C64" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D64" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E64">
         <v>6</v>
       </c>
       <c r="F64" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G64" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H64" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I64">
-        <v>2800</v>
+        <v>4440</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>3.5329733330000002</v>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N64" s="1">
-        <v>45216</v>
-      </c>
-      <c r="O64" s="1">
-        <v>45581</v>
+        <v>45214</v>
       </c>
       <c r="P64" s="1">
-        <v>45305</v>
-      </c>
-      <c r="R64" s="1">
-        <v>45117</v>
+        <v>45303</v>
       </c>
       <c r="T64" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
@@ -4564,55 +4600,49 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>6589</v>
+        <v>1459</v>
       </c>
       <c r="C65" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F65" t="s">
         <v>37</v>
       </c>
       <c r="G65" t="s">
-        <v>38</v>
+        <v>186</v>
       </c>
       <c r="H65" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I65">
-        <v>2800</v>
+        <v>4727</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>16.385896670000001</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M65" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N65" s="1">
-        <v>45874</v>
-      </c>
-      <c r="O65" s="1">
-        <v>46238</v>
+        <v>45231</v>
       </c>
       <c r="P65" s="1">
-        <v>45963</v>
-      </c>
-      <c r="S65" s="1">
-        <v>48500</v>
+        <v>45320</v>
       </c>
       <c r="T65" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.25">
@@ -4620,55 +4650,49 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>5128</v>
+        <v>1473</v>
       </c>
       <c r="C66" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F66" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G66" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H66" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I66">
-        <v>2800</v>
+        <v>4837</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>4.9613533329999999</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M66" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N66" s="1">
-        <v>44808</v>
-      </c>
-      <c r="O66" s="1">
-        <v>45172</v>
+        <v>45245</v>
       </c>
       <c r="P66" s="1">
-        <v>44898</v>
-      </c>
-      <c r="R66" s="1">
-        <v>46319</v>
+        <v>45334</v>
       </c>
       <c r="T66" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
@@ -4676,49 +4700,55 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>6675</v>
+        <v>1512</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D67" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H67" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I67">
-        <v>2800</v>
+        <v>3250</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>32.353326670000001</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M67" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N67" s="1">
-        <v>46204</v>
+        <v>45281</v>
+      </c>
+      <c r="O67" s="1">
+        <v>46625</v>
       </c>
       <c r="P67" s="1">
-        <v>46203</v>
+        <v>45459</v>
+      </c>
+      <c r="R67" s="1">
+        <v>46569</v>
       </c>
       <c r="T67" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
@@ -4726,52 +4756,49 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>2650</v>
+        <v>1860</v>
       </c>
       <c r="C68" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D68" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F68" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G68" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H68" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I68">
-        <v>2800</v>
+        <v>4617</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>14.598466670000001</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M68" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N68" s="1">
-        <v>46244</v>
+        <v>45627</v>
       </c>
       <c r="P68" s="1">
-        <v>46243</v>
-      </c>
-      <c r="R68" s="1">
-        <v>46216</v>
+        <v>45716</v>
       </c>
       <c r="T68" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
@@ -4779,52 +4806,49 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>2649</v>
+        <v>1927</v>
       </c>
       <c r="C69" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G69" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="H69" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I69">
-        <v>2800</v>
+        <v>4507</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>10.56653</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M69" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N69" s="1">
-        <v>46244</v>
+        <v>45691</v>
       </c>
       <c r="P69" s="1">
-        <v>46243</v>
-      </c>
-      <c r="R69" s="1">
-        <v>45729</v>
+        <v>45780</v>
       </c>
       <c r="T69" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
@@ -4832,55 +4856,52 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>6166</v>
+        <v>1928</v>
       </c>
       <c r="C70" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D70" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G70" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="H70" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="I70">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>2.51586</v>
       </c>
       <c r="K70">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M70" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="N70" s="1">
-        <v>45658</v>
-      </c>
-      <c r="O70" s="1">
-        <v>46022</v>
+        <v>45697</v>
       </c>
       <c r="P70" s="1">
-        <v>45747</v>
+        <v>45786</v>
       </c>
       <c r="R70" s="1">
-        <v>45661</v>
+        <v>46394</v>
       </c>
       <c r="T70" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.25">
@@ -4888,49 +4909,49 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>7287</v>
+        <v>1935</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="H71" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I71">
-        <v>2800</v>
+        <v>4507</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>11.574593330000001</v>
       </c>
       <c r="K71">
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M71" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N71" s="1">
-        <v>46223</v>
+        <v>45698</v>
       </c>
       <c r="P71" s="1">
-        <v>46222</v>
+        <v>45787</v>
       </c>
       <c r="T71" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
@@ -4938,49 +4959,49 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>7288</v>
+        <v>1939</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D72" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F72" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G72" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="H72" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I72">
-        <v>2800</v>
+        <v>4617</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>10.136846670000001</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M72" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N72" s="1">
-        <v>46219</v>
+        <v>45698</v>
       </c>
       <c r="P72" s="1">
-        <v>46218</v>
+        <v>45787</v>
       </c>
       <c r="T72" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
@@ -4988,49 +5009,49 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>7289</v>
+        <v>1940</v>
       </c>
       <c r="C73" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D73" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F73" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="H73" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I73">
-        <v>2800</v>
+        <v>4617</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>20.63170667</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M73" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N73" s="1">
-        <v>46219</v>
+        <v>45701</v>
       </c>
       <c r="P73" s="1">
-        <v>46218</v>
+        <v>45790</v>
       </c>
       <c r="T73" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
@@ -5038,49 +5059,49 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>7291</v>
+        <v>1941</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D74" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F74" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G74" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H74" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I74">
-        <v>2800</v>
+        <v>4617</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>26.689769999999999</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M74" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N74" s="1">
-        <v>46219</v>
+        <v>45706</v>
       </c>
       <c r="P74" s="1">
-        <v>46218</v>
+        <v>45795</v>
       </c>
       <c r="T74" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
@@ -5088,49 +5109,49 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>7292</v>
+        <v>1971</v>
       </c>
       <c r="C75" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D75" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E75">
         <v>6</v>
       </c>
       <c r="F75" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G75" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="H75" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I75">
-        <v>2800</v>
+        <v>4220</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>19.018149999999999</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M75" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N75" s="1">
-        <v>46219</v>
+        <v>45724</v>
       </c>
       <c r="P75" s="1">
-        <v>46218</v>
+        <v>45813</v>
       </c>
       <c r="T75" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
@@ -5138,49 +5159,49 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>7293</v>
+        <v>1972</v>
       </c>
       <c r="C76" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D76" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G76" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="H76" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I76">
-        <v>2800</v>
+        <v>4617</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>26.823643329999999</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M76" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N76" s="1">
-        <v>46219</v>
+        <v>45721</v>
       </c>
       <c r="P76" s="1">
-        <v>46218</v>
+        <v>45810</v>
       </c>
       <c r="T76" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
@@ -5188,49 +5209,49 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>7294</v>
+        <v>2078</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D77" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G77" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="H77" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I77">
-        <v>2800</v>
+        <v>4617</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>16.338149999999999</v>
       </c>
       <c r="K77">
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M77" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N77" s="1">
-        <v>46219</v>
+        <v>45858</v>
       </c>
       <c r="P77" s="1">
-        <v>46218</v>
+        <v>46038</v>
       </c>
       <c r="T77" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
@@ -5238,49 +5259,49 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>7295</v>
+        <v>2298</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D78" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F78" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G78" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H78" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I78">
-        <v>2800</v>
+        <v>4287</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>11.49202333</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M78" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N78" s="1">
-        <v>46219</v>
+        <v>46026</v>
       </c>
       <c r="P78" s="1">
-        <v>46218</v>
+        <v>46204</v>
       </c>
       <c r="T78" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
@@ -5288,52 +5309,58 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>7300</v>
+        <v>2350</v>
       </c>
       <c r="C79" t="s">
+        <v>218</v>
+      </c>
+      <c r="D79" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79">
+        <v>5</v>
+      </c>
+      <c r="F79" t="s">
+        <v>49</v>
+      </c>
+      <c r="G79" t="s">
+        <v>220</v>
+      </c>
+      <c r="H79" t="s">
+        <v>199</v>
+      </c>
+      <c r="I79">
+        <v>3000</v>
+      </c>
+      <c r="J79">
+        <v>29.5472</v>
+      </c>
+      <c r="K79">
+        <v>4.5</v>
+      </c>
+      <c r="L79" t="s">
+        <v>24</v>
+      </c>
+      <c r="M79" t="s">
         <v>221</v>
       </c>
-      <c r="D79" t="s">
-        <v>222</v>
-      </c>
-      <c r="E79">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>46</v>
-      </c>
-      <c r="G79" t="s">
-        <v>223</v>
-      </c>
-      <c r="H79" t="s">
-        <v>174</v>
-      </c>
-      <c r="I79">
-        <v>2800</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79" t="s">
-        <v>23</v>
-      </c>
-      <c r="M79" t="s">
-        <v>40</v>
-      </c>
       <c r="N79" s="1">
-        <v>46218</v>
+        <v>45904</v>
       </c>
       <c r="O79" s="1">
-        <v>46582</v>
+        <v>46633</v>
       </c>
       <c r="P79" s="1">
-        <v>46307</v>
+        <v>45993</v>
+      </c>
+      <c r="R79" s="1">
+        <v>46623</v>
+      </c>
+      <c r="S79" s="1">
+        <v>48850</v>
       </c>
       <c r="T79" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
@@ -5341,49 +5368,49 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>7301</v>
+        <v>2443</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D80" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E80">
         <v>6</v>
       </c>
       <c r="F80" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H80" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I80">
-        <v>2800</v>
+        <v>4001</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>13.37832</v>
       </c>
       <c r="K80">
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M80" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N80" s="1">
-        <v>46218</v>
+        <v>46167</v>
       </c>
       <c r="P80" s="1">
-        <v>46217</v>
+        <v>46345</v>
       </c>
       <c r="T80" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.25">
@@ -5391,49 +5418,49 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>7302</v>
+        <v>2444</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D81" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F81" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G81" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="H81" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="I81">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>11.76796667</v>
       </c>
       <c r="K81">
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="M81" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N81" s="1">
-        <v>46218</v>
+        <v>46194</v>
       </c>
       <c r="P81" s="1">
-        <v>46217</v>
+        <v>46372</v>
       </c>
       <c r="T81" t="s">
-        <v>224</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.25">
@@ -5441,55 +5468,49 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>6233</v>
+        <v>2445</v>
       </c>
       <c r="C82" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D82" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F82" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G82" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="H82" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I82">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>8.2105366669999995</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="M82" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N82" s="1">
-        <v>45717</v>
-      </c>
-      <c r="O82" s="1">
-        <v>46081</v>
+        <v>46200</v>
       </c>
       <c r="P82" s="1">
-        <v>45806</v>
-      </c>
-      <c r="R82" s="1">
-        <v>45719</v>
+        <v>46378</v>
       </c>
       <c r="T82" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.25">
@@ -5497,55 +5518,49 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>6234</v>
+        <v>2447</v>
       </c>
       <c r="C83" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D83" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E83">
         <v>6</v>
       </c>
       <c r="F83" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G83" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="H83" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I83">
-        <v>2800</v>
+        <v>4001</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>10.90085333</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M83" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N83" s="1">
-        <v>45717</v>
-      </c>
-      <c r="O83" s="1">
-        <v>46081</v>
+        <v>46208</v>
       </c>
       <c r="P83" s="1">
-        <v>45806</v>
-      </c>
-      <c r="R83" s="1">
-        <v>45746</v>
+        <v>46389</v>
       </c>
       <c r="T83" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.25">
@@ -5553,55 +5568,49 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>6235</v>
+        <v>2448</v>
       </c>
       <c r="C84" t="s">
+        <v>232</v>
+      </c>
+      <c r="D84" t="s">
         <v>233</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84">
+        <v>5</v>
+      </c>
+      <c r="F84" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" t="s">
         <v>234</v>
       </c>
-      <c r="E84">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>66</v>
-      </c>
-      <c r="G84" t="s">
-        <v>164</v>
-      </c>
       <c r="H84" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I84">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>10.65310667</v>
       </c>
       <c r="K84">
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M84" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N84" s="1">
-        <v>45717</v>
-      </c>
-      <c r="O84" s="1">
-        <v>46081</v>
+        <v>46212</v>
       </c>
       <c r="P84" s="1">
-        <v>45806</v>
-      </c>
-      <c r="R84" s="1">
-        <v>45718</v>
+        <v>46396</v>
       </c>
       <c r="T84" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.25">
@@ -5609,7 +5618,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>6236</v>
+        <v>2449</v>
       </c>
       <c r="C85" t="s">
         <v>235</v>
@@ -5618,46 +5627,40 @@
         <v>236</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F85" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G85" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="H85" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I85">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>10.71504333</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M85" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N85" s="1">
-        <v>45717</v>
-      </c>
-      <c r="O85" s="1">
-        <v>46081</v>
+        <v>46211</v>
       </c>
       <c r="P85" s="1">
-        <v>45806</v>
-      </c>
-      <c r="R85" s="1">
-        <v>45440</v>
+        <v>46392</v>
       </c>
       <c r="T85" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.25">
@@ -5665,7 +5668,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>6237</v>
+        <v>2451</v>
       </c>
       <c r="C86" t="s">
         <v>237</v>
@@ -5674,46 +5677,40 @@
         <v>238</v>
       </c>
       <c r="E86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F86" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G86" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="H86" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I86">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>10.65310667</v>
       </c>
       <c r="K86">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M86" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N86" s="1">
-        <v>45717</v>
-      </c>
-      <c r="O86" s="1">
-        <v>46081</v>
+        <v>46212</v>
       </c>
       <c r="P86" s="1">
-        <v>45806</v>
-      </c>
-      <c r="R86" s="1">
-        <v>46089</v>
+        <v>46393</v>
       </c>
       <c r="T86" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.25">
@@ -5721,7 +5718,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>6450</v>
+        <v>2452</v>
       </c>
       <c r="C87" t="s">
         <v>239</v>
@@ -5733,40 +5730,37 @@
         <v>6</v>
       </c>
       <c r="F87" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G87" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="H87" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I87">
-        <v>2800</v>
+        <v>4001</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>9.9718033330000004</v>
       </c>
       <c r="K87">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M87" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N87" s="1">
-        <v>45854</v>
-      </c>
-      <c r="O87" s="1">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="P87" s="1">
-        <v>45943</v>
+        <v>46402</v>
       </c>
       <c r="T87" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.25">
@@ -5774,7 +5768,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>6455</v>
+        <v>2454</v>
       </c>
       <c r="C88" t="s">
         <v>241</v>
@@ -5783,43 +5777,40 @@
         <v>242</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F88" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="G88" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="H88" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I88">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>9.2904999999999998</v>
       </c>
       <c r="K88">
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="M88" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N88" s="1">
-        <v>45854</v>
-      </c>
-      <c r="O88" s="1">
-        <v>46218</v>
+        <v>46235</v>
       </c>
       <c r="P88" s="1">
-        <v>45943</v>
+        <v>46413</v>
       </c>
       <c r="T88" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.25">
@@ -5827,7 +5818,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>6459</v>
+        <v>2463</v>
       </c>
       <c r="C89" t="s">
         <v>243</v>
@@ -5836,46 +5827,40 @@
         <v>244</v>
       </c>
       <c r="E89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G89" t="s">
-        <v>43</v>
+        <v>174</v>
       </c>
       <c r="H89" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I89">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>16.949770000000001</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M89" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N89" s="1">
-        <v>45854</v>
-      </c>
-      <c r="O89" s="1">
-        <v>46218</v>
+        <v>45953</v>
       </c>
       <c r="P89" s="1">
-        <v>45943</v>
-      </c>
-      <c r="S89" s="1">
-        <v>48602</v>
+        <v>46131</v>
       </c>
       <c r="T89" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
@@ -5883,7 +5868,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>6460</v>
+        <v>2474</v>
       </c>
       <c r="C90" t="s">
         <v>245</v>
@@ -5895,40 +5880,37 @@
         <v>6</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G90" t="s">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="H90" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I90">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>9.9562133330000009</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M90" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N90" s="1">
-        <v>45854</v>
-      </c>
-      <c r="O90" s="1">
-        <v>46218</v>
+        <v>45963</v>
       </c>
       <c r="P90" s="1">
-        <v>45943</v>
+        <v>46141</v>
       </c>
       <c r="T90" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
@@ -5936,7 +5918,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>6587</v>
+        <v>2669</v>
       </c>
       <c r="C91" t="s">
         <v>247</v>
@@ -5945,43 +5927,40 @@
         <v>248</v>
       </c>
       <c r="E91">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G91" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="H91" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="I91">
-        <v>2800</v>
+        <v>4397</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>13.167833330000001</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M91" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N91" s="1">
-        <v>45874</v>
-      </c>
-      <c r="O91" s="1">
-        <v>46238</v>
+        <v>45998</v>
       </c>
       <c r="P91" s="1">
-        <v>45963</v>
+        <v>46176</v>
       </c>
       <c r="T91" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
@@ -5989,7 +5968,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>6674</v>
+        <v>2693</v>
       </c>
       <c r="C92" t="s">
         <v>249</v>
@@ -5998,40 +5977,40 @@
         <v>250</v>
       </c>
       <c r="E92">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92" t="s">
         <v>37</v>
       </c>
       <c r="G92" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="H92" t="s">
-        <v>251</v>
+        <v>183</v>
       </c>
       <c r="I92">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>13.386176669999999</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M92" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N92" s="1">
-        <v>45992</v>
+        <v>46056</v>
       </c>
       <c r="P92" s="1">
-        <v>45991</v>
+        <v>46234</v>
       </c>
       <c r="T92" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
@@ -6039,52 +6018,49 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>7648</v>
+        <v>2708</v>
       </c>
       <c r="C93" t="s">
+        <v>251</v>
+      </c>
+      <c r="D93" t="s">
         <v>252</v>
-      </c>
-      <c r="D93" t="s">
-        <v>253</v>
       </c>
       <c r="E93">
         <v>6</v>
       </c>
       <c r="F93" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G93" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="H93" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I93">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>13.99768667</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M93" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N93" s="1">
-        <v>46244</v>
+        <v>46157</v>
       </c>
       <c r="P93" s="1">
-        <v>46243</v>
-      </c>
-      <c r="R93" s="1">
-        <v>46113</v>
+        <v>46335</v>
       </c>
       <c r="T93" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.25">
@@ -6092,49 +6068,49 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>8008</v>
+        <v>2772</v>
       </c>
       <c r="C94" t="s">
+        <v>253</v>
+      </c>
+      <c r="D94" t="s">
         <v>254</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94">
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" t="s">
         <v>255</v>
       </c>
-      <c r="E94">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>32</v>
-      </c>
-      <c r="G94" t="s">
-        <v>43</v>
-      </c>
       <c r="H94" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="I94">
-        <v>2800</v>
+        <v>4947</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>7.4324000000000003</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M94" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N94" s="1">
-        <v>46305</v>
-      </c>
-      <c r="R94" s="1">
-        <v>46377</v>
+        <v>46266</v>
+      </c>
+      <c r="P94" s="1">
+        <v>46355</v>
       </c>
       <c r="T94" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.25">
@@ -6142,7 +6118,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>7277</v>
+        <v>2773</v>
       </c>
       <c r="C95" t="s">
         <v>256</v>
@@ -6154,40 +6130,37 @@
         <v>6</v>
       </c>
       <c r="F95" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G95" t="s">
-        <v>38</v>
+        <v>224</v>
       </c>
       <c r="H95" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I95">
-        <v>2800</v>
+        <v>4001</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <v>7.4324000000000003</v>
       </c>
       <c r="K95">
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M95" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N95" s="1">
-        <v>46143</v>
-      </c>
-      <c r="O95" s="1">
-        <v>46507</v>
+        <v>46266</v>
       </c>
       <c r="P95" s="1">
-        <v>46232</v>
+        <v>46355</v>
       </c>
       <c r="T95" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.25">
@@ -6195,7 +6168,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>7278</v>
+        <v>2778</v>
       </c>
       <c r="C96" t="s">
         <v>258</v>
@@ -6207,40 +6180,37 @@
         <v>6</v>
       </c>
       <c r="F96" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G96" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="H96" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I96">
-        <v>2800</v>
+        <v>4001</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>7.1227166669999997</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M96" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N96" s="1">
-        <v>46143</v>
-      </c>
-      <c r="O96" s="1">
-        <v>46507</v>
+        <v>46266</v>
       </c>
       <c r="P96" s="1">
-        <v>46232</v>
+        <v>46355</v>
       </c>
       <c r="T96" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.25">
@@ -6248,7 +6218,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>7286</v>
+        <v>2780</v>
       </c>
       <c r="C97" t="s">
         <v>260</v>
@@ -6257,40 +6227,40 @@
         <v>261</v>
       </c>
       <c r="E97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G97" t="s">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="H97" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="I97">
-        <v>2800</v>
+        <v>4001</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>5.5743</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M97" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="N97" s="1">
-        <v>46219</v>
+        <v>46296</v>
       </c>
       <c r="P97" s="1">
-        <v>46218</v>
+        <v>46385</v>
       </c>
       <c r="T97" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
